--- a/7 semester/SMAD/lab1/Lab1-salary.xlsx
+++ b/7 semester/SMAD/lab1/Lab1-salary.xlsx
@@ -1,18 +1,57 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sasha\BSUIR\7 semester\SMAD\lab1\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67C55AE5-4BF4-4383-9237-9B28ABDDF700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="32362" windowHeight="17955" activeTab="1"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="10218000003" sheetId="1" r:id="rId1"/>
     <sheet name="Лист2" sheetId="2" r:id="rId2"/>
     <sheet name="Лист3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -603,14 +642,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="27">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -623,6 +656,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
@@ -631,6 +665,7 @@
       <sz val="11"/>
       <color theme="4" tint="-0.249977111117893"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
@@ -638,6 +673,7 @@
       <sz val="11"/>
       <color theme="4" tint="-0.249977111117893"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
@@ -645,172 +681,24 @@
       <b/>
       <sz val="14"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -819,198 +707,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor theme="4" tint="0.799981688894314"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="4" tint="0.79995117038483843"/>
+        <bgColor theme="4" tint="0.79995117038483843"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -1147,251 +849,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="15" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1438,61 +898,759 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
-    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
-    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
-    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
-    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
-    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
-    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
-    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
-    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
-    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
-    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
-    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
-    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
-    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
-    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
-    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
-    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
-    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
-    <cellStyle name="Total" xfId="25" builtinId="25"/>
-    <cellStyle name="Output" xfId="26" builtinId="21"/>
-    <cellStyle name="Currency" xfId="27" builtinId="4"/>
-    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
-    <cellStyle name="Note" xfId="29" builtinId="10"/>
-    <cellStyle name="Input" xfId="30" builtinId="20"/>
-    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
-    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
-    <cellStyle name="Good" xfId="33" builtinId="26"/>
-    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
-    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
-    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
-    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
-    <cellStyle name="Title" xfId="39" builtinId="15"/>
-    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
-    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
-    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
-    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
-    <cellStyle name="Comma" xfId="44" builtinId="3"/>
-    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
-    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
-    <cellStyle name="Percent" xfId="47" builtinId="5"/>
-    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
+  <cellStyles count="1">
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="32">
+  <dxfs count="52">
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <border>
         <left/>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left/>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left/>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left/>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
         <right style="thin">
           <color auto="1"/>
         </right>
@@ -1520,485 +1678,11 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border>
         <left/>
         <right style="thin">
           <color auto="1"/>
         </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left/>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left/>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left/>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right/>
         <top style="thin">
           <color auto="1"/>
         </top>
@@ -2013,14 +1697,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="zh-CN"/>
+  <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2062,7 +1749,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2071,6 +1757,26 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -2094,9 +1800,6 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
           <c:cat>
             <c:numRef>
               <c:extLst>
@@ -2123,7 +1826,7 @@
                   <c:v>2416.11</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2606.05</c:v>
+                  <c:v>2606.0500000000002</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>2795.99</c:v>
@@ -2183,6 +1886,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3DE6-4575-8E05-DA9B087ABB2D}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -2227,9 +1935,6 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
           <c:cat>
             <c:numRef>
               <c:extLst>
@@ -2256,7 +1961,7 @@
                   <c:v>2416.11</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2606.05</c:v>
+                  <c:v>2606.0500000000002</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>2795.99</c:v>
@@ -2317,6 +2022,11 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-3DE6-4575-8E05-DA9B087ABB2D}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -2365,7 +2075,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -2374,6 +2083,26 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ru-RU"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -2409,6 +2138,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1139151072"/>
@@ -2470,7 +2200,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -2479,6 +2208,26 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ru-RU"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -2508,6 +2257,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1139151552"/>
@@ -2548,6 +2298,7 @@
       <a:pPr>
         <a:defRPr lang="en-US"/>
       </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -2559,9 +2310,9 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="zh-CN"/>
+  <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2573,7 +2324,6 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2599,6 +2349,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -2635,9 +2386,6 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:dLbls>
-            <c:delete val="1"/>
-          </c:dLbls>
           <c:cat>
             <c:numRef>
               <c:extLst>
@@ -2664,7 +2412,7 @@
                   <c:v>2416.11</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2606.05</c:v>
+                  <c:v>2606.0500000000002</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>2795.99</c:v>
@@ -2725,6 +2473,11 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7B58-4E4C-8B11-885D37BC76AA}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -2780,6 +2533,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1690012783"/>
@@ -2838,6 +2592,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1868277055"/>
@@ -2878,6 +2633,7 @@
       <a:pPr>
         <a:defRPr lang="en-US"/>
       </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -3975,7 +3731,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
@@ -3991,13 +3747,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4029,13 +3791,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPr id="3" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4056,7 +3824,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
@@ -4070,14 +3838,20 @@
       <xdr:row>29</xdr:row>
       <xdr:rowOff>180000</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Диаграмма 1"/>
+        <xdr:cNvPr id="2" name="Диаграмма 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="10325100" y="2423795"/>
-        <a:ext cx="6097905" cy="3133090"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -4100,14 +3874,20 @@
       <xdr:row>27</xdr:row>
       <xdr:rowOff>161432</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Диаграмма 4"/>
+        <xdr:cNvPr id="5" name="Диаграмма 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="17205325" y="2422525"/>
-        <a:ext cx="4912360" cy="2745105"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -4121,81 +3901,133 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Таблица2" displayName="Таблица2" ref="A2:E131" totalsRowShown="0">
-  <autoFilter ref="A2:E131"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Таблица2" displayName="Таблица2" ref="A2:E131" totalsRowShown="0">
+  <autoFilter ref="A2:E131" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="5">
-    <tableColumn id="1" name="Территория Республики Беларусь" dataDxfId="0"/>
-    <tableColumn id="6" name="Группа" dataDxfId="1"/>
-    <tableColumn id="2" name="2025" dataDxfId="2"/>
-    <tableColumn id="5" name="ln_2025" dataDxfId="3"/>
-    <tableColumn id="3" name="Выброс?" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Территория Республики Беларусь" dataDxfId="51"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Группа" dataDxfId="50">
+      <calculatedColumnFormula>MATCH(Таблица2[[#This Row],[2025]],Таблица3[Ниж. Гран],1)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="2025" dataDxfId="49"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="ln_2025" dataDxfId="48">
+      <calculatedColumnFormula>LN(Таблица2[[#This Row],[2025]])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Выброс?" dataDxfId="47">
+      <calculatedColumnFormula>IF(OR(C3&gt;3*$G$4,C3&lt;$G$4/3),"ВЫБРОС","ОК")</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Таблица3" displayName="Таблица3" ref="I2:R12" totalsRowCount="1">
-  <autoFilter ref="I2:R11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Таблица3" displayName="Таблица3" ref="I2:R12" totalsRowCount="1">
+  <autoFilter ref="I2:R11" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="10">
-    <tableColumn id="1" name="Интервал" totalsRowLabel="Итог" dataDxfId="5"/>
-    <tableColumn id="2" name="Ниж. Гран" totalsRowFunction="sum" dataDxfId="6"/>
-    <tableColumn id="3" name="Верх. Гран." totalsRowFunction="sum" dataDxfId="7"/>
-    <tableColumn id="4" name="Середина" totalsRowFunction="sum" dataDxfId="8"/>
-    <tableColumn id="5" name="Частота" totalsRowFunction="sum" dataDxfId="9"/>
-    <tableColumn id="6" name="Отн. Частота" totalsRowFunction="sum" dataDxfId="10"/>
-    <tableColumn id="7" name="накопл" dataDxfId="11"/>
-    <tableColumn id="9" name="F(b_i)" dataDxfId="12"/>
-    <tableColumn id="10" name="тервер(р_i)" dataDxfId="13"/>
-    <tableColumn id="8" name="тервер(n''_i)" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Интервал" totalsRowLabel="Итог" dataDxfId="46" totalsRowDxfId="45"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Ниж. Гран" totalsRowFunction="sum" dataDxfId="44" totalsRowDxfId="43">
+      <calculatedColumnFormula>K2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Верх. Гран." totalsRowFunction="sum" dataDxfId="42" totalsRowDxfId="41">
+      <calculatedColumnFormula>J3+$G$15</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Середина" totalsRowFunction="sum" dataDxfId="40" totalsRowDxfId="39">
+      <calculatedColumnFormula>ROUND((Таблица3[[#This Row],[Ниж. Гран]]+Таблица3[[#This Row],[Верх. Гран.]])/2,2)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Частота" totalsRowFunction="sum" dataDxfId="38" totalsRowDxfId="37">
+      <calculatedColumnFormula>IF(Таблица3[[#This Row],[Интервал]]=MAX(Таблица3[Интервал]),COUNTIFS(Таблица2[2025],"&gt;="&amp;Таблица3[[#This Row],[Ниж. Гран]],Таблица2[2025],"&lt;="&amp;Таблица3[[#This Row],[Верх. Гран.]]),COUNTIFS(Таблица2[2025],"&gt;="&amp;Таблица3[[#This Row],[Ниж. Гран]],Таблица2[2025],"&lt;"&amp;Таблица3[[#This Row],[Верх. Гран.]]))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Отн. Частота" totalsRowFunction="sum" dataDxfId="36" totalsRowDxfId="35">
+      <calculatedColumnFormula>Таблица3[[#This Row],[Частота]]/$G$2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="накопл" dataDxfId="34" totalsRowDxfId="33">
+      <calculatedColumnFormula>O2+Таблица3[[#This Row],[Частота]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="F(b_i)" dataDxfId="32" totalsRowDxfId="31">
+      <calculatedColumnFormula>_xlfn.LOGNORM.DIST(Таблица3[[#This Row],[Верх. Гран.]],$U$4,$U$5,TRUE)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="тервер(р_i)" dataDxfId="30">
+      <calculatedColumnFormula>1-_xlfn.LOGNORM.DIST(Таблица3[[#This Row],[Ниж. Гран]],$U$4,$U$5,TRUE)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="тервер(n''_i)" dataDxfId="29">
+      <calculatedColumnFormula>Таблица3[[#This Row],[тервер(р_i)]]*$G$2</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Таблица35" displayName="Таблица35" ref="I33:N42" totalsRowCount="1">
-  <autoFilter ref="I33:N41"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Таблица35" displayName="Таблица35" ref="I33:N42" totalsRowCount="1">
+  <autoFilter ref="I33:N41" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="Интервал" totalsRowLabel="Итог" dataDxfId="15"/>
-    <tableColumn id="2" name="Ниж. Гран" totalsRowFunction="sum" dataDxfId="16"/>
-    <tableColumn id="3" name="Верх. Гран." totalsRowFunction="sum" dataDxfId="17"/>
-    <tableColumn id="4" name="Середина" totalsRowFunction="sum" dataDxfId="18"/>
-    <tableColumn id="5" name="Частота" totalsRowFunction="sum" dataDxfId="19"/>
-    <tableColumn id="6" name="Отн. Частота" totalsRowFunction="sum" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Интервал" totalsRowLabel="Итог" dataDxfId="28" totalsRowDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Ниж. Гран" totalsRowFunction="sum" dataDxfId="27" totalsRowDxfId="11">
+      <calculatedColumnFormula>K33</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Верх. Гран." totalsRowFunction="sum" dataDxfId="26" totalsRowDxfId="10">
+      <calculatedColumnFormula>J34+$G$35</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Середина" totalsRowFunction="sum" dataDxfId="25" totalsRowDxfId="9">
+      <calculatedColumnFormula>ROUND((Таблица35[[#This Row],[Ниж. Гран]]+Таблица35[[#This Row],[Верх. Гран.]])/2,2)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Частота" totalsRowFunction="sum" dataDxfId="24" totalsRowDxfId="8">
+      <calculatedColumnFormula>IF(Таблица35[[#This Row],[Интервал]]=MAX(Таблица35[Интервал]),COUNTIFS(Таблица2[2025],"&gt;="&amp;Таблица35[[#This Row],[Ниж. Гран]],Таблица2[2025],"&lt;="&amp;Таблица35[[#This Row],[Верх. Гран.]]),COUNTIFS(Таблица2[2025],"&gt;="&amp;Таблица35[[#This Row],[Ниж. Гран]],Таблица2[2025],"&lt;"&amp;Таблица35[[#This Row],[Верх. Гран.]]))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Отн. Частота" totalsRowFunction="sum" dataDxfId="23" totalsRowDxfId="7">
+      <calculatedColumnFormula>Таблица35[[#This Row],[Частота]]/$G$2</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Таблица356" displayName="Таблица356" ref="I62:N73" totalsRowCount="1">
-  <autoFilter ref="I62:N72"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Таблица356" displayName="Таблица356" ref="I62:N73" totalsRowCount="1">
+  <autoFilter ref="I62:N72" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="Интервал" totalsRowLabel="Итог" dataDxfId="21"/>
-    <tableColumn id="2" name="Ниж. Гран" totalsRowFunction="sum" dataDxfId="22"/>
-    <tableColumn id="3" name="Верх. Гран." totalsRowFunction="sum" dataDxfId="23"/>
-    <tableColumn id="4" name="Середина" totalsRowFunction="sum" dataDxfId="24"/>
-    <tableColumn id="5" name="Частота" totalsRowFunction="sum" dataDxfId="25"/>
-    <tableColumn id="6" name="Отн. Частота" totalsRowFunction="sum" dataDxfId="26"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Интервал" totalsRowLabel="Итог" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Ниж. Гран" totalsRowFunction="sum" dataDxfId="21">
+      <calculatedColumnFormula>K62</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Верх. Гран." totalsRowFunction="sum" dataDxfId="20">
+      <calculatedColumnFormula>J63+$G$64</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Середина" totalsRowFunction="sum" dataDxfId="19">
+      <calculatedColumnFormula>ROUND((Таблица356[[#This Row],[Ниж. Гран]]+Таблица356[[#This Row],[Верх. Гран.]])/2,2)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Частота" totalsRowFunction="sum" dataDxfId="18">
+      <calculatedColumnFormula>IF(Таблица356[[#This Row],[Интервал]]=MAX(Таблица356[Интервал]),COUNTIFS(Таблица2[2025],"&gt;="&amp;Таблица356[[#This Row],[Ниж. Гран]],Таблица2[2025],"&lt;="&amp;Таблица356[[#This Row],[Верх. Гран.]]),COUNTIFS(Таблица2[2025],"&gt;="&amp;Таблица356[[#This Row],[Ниж. Гран]],Таблица2[2025],"&lt;"&amp;Таблица356[[#This Row],[Верх. Гран.]]))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Отн. Частота" totalsRowFunction="sum" dataDxfId="17">
+      <calculatedColumnFormula>Таблица356[[#This Row],[Частота]]/$G$2</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Таблица1" displayName="Таблица1" ref="Y20:AD30" totalsRowCount="1">
-  <autoFilter ref="Y20:AD29"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Таблица1" displayName="Таблица1" ref="Y20:AD30" totalsRowCount="1">
+  <autoFilter ref="Y20:AD29" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="группа" totalsRowLabel="Итог" dataDxfId="27"/>
-    <tableColumn id="2" name="частота" dataDxfId="28"/>
-    <tableColumn id="3" name="групп сред" dataDxfId="29"/>
-    <tableColumn id="4" name="групп дисп" dataDxfId="30"/>
-    <tableColumn id="5" name="взвеш дисп" totalsRowFunction="custom">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="группа" totalsRowLabel="Итог" dataDxfId="16" totalsRowDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="частота" dataDxfId="15" totalsRowDxfId="4">
+      <calculatedColumnFormula>M3</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="групп сред" dataDxfId="14" totalsRowDxfId="3">
+      <calculatedColumnFormula>AVERAGEIF(Таблица2[Группа],Таблица1[[#This Row],[группа]],Таблица2[2025])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="групп дисп" dataDxfId="6" totalsRowDxfId="2">
+      <calculatedColumnFormula array="1">_xlfn.VAR.P(_xlfn._xlws.FILTER(Таблица2[2025],Таблица2[Группа]=Таблица1[[#This Row],[группа]]))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="взвеш дисп" totalsRowFunction="custom" totalsRowDxfId="1">
       <calculatedColumnFormula>SUM(Таблица1[взвеш дисп])</calculatedColumnFormula>
       <totalsRowFormula>SUM(Таблица1[взвеш дисп])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" name="взвеш кв откл" totalsRowFunction="sum" dataDxfId="31"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="взвеш кв откл" totalsRowFunction="sum" dataDxfId="13" totalsRowDxfId="0">
+      <calculatedColumnFormula>Таблица1[[#This Row],[частота]]*(Таблица1[[#This Row],[групп сред]]-$G$3)^2</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4482,30 +4314,30 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B144"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.6" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="2" width="30.9203539823009" customWidth="1"/>
+    <col min="1" max="2" width="30.921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="43.5" customHeight="1"/>
-    <row r="4" ht="17.6" spans="1:1">
+    <row r="1" spans="1:2" ht="43.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="4" spans="1:2" ht="17.600000000000001" x14ac:dyDescent="0.4">
       <c r="A4" s="23" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B6" s="24" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" s="25" t="s">
         <v>2</v>
       </c>
@@ -4513,7 +4345,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" s="26" t="s">
         <v>4</v>
       </c>
@@ -4521,7 +4353,7 @@
         <v>2679.7</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" s="26" t="s">
         <v>5</v>
       </c>
@@ -4529,15 +4361,15 @@
         <v>2360.4</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" s="26" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="26">
-        <v>2270.2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>2270.1999999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" s="26" t="s">
         <v>7</v>
       </c>
@@ -4545,7 +4377,7 @@
         <v>2427</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" s="26" t="s">
         <v>8</v>
       </c>
@@ -4553,7 +4385,7 @@
         <v>2502</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" s="26" t="s">
         <v>9</v>
       </c>
@@ -4561,7 +4393,7 @@
         <v>1971.8</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" s="26" t="s">
         <v>10</v>
       </c>
@@ -4569,7 +4401,7 @@
         <v>2132.1</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" s="26" t="s">
         <v>11</v>
       </c>
@@ -4577,7 +4409,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" s="26" t="s">
         <v>12</v>
       </c>
@@ -4585,7 +4417,7 @@
         <v>2260</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" s="26" t="s">
         <v>13</v>
       </c>
@@ -4593,39 +4425,39 @@
         <v>2114.6</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" s="26" t="s">
         <v>14</v>
       </c>
       <c r="B18" s="26">
-        <v>2399.3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
+        <v>2399.3000000000002</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" s="26" t="s">
         <v>15</v>
       </c>
       <c r="B19" s="26">
-        <v>2285.7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
+        <v>2285.6999999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" s="26" t="s">
         <v>16</v>
       </c>
       <c r="B20" s="26">
-        <v>2211.2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
+        <v>2211.1999999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" s="26" t="s">
         <v>17</v>
       </c>
       <c r="B21" s="26">
-        <v>2128.7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
+        <v>2128.6999999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" s="26" t="s">
         <v>18</v>
       </c>
@@ -4633,7 +4465,7 @@
         <v>2137.5</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" s="26" t="s">
         <v>19</v>
       </c>
@@ -4641,7 +4473,7 @@
         <v>2217.6</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" s="26" t="s">
         <v>20</v>
       </c>
@@ -4649,7 +4481,7 @@
         <v>2293.5</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" s="26" t="s">
         <v>21</v>
       </c>
@@ -4657,7 +4489,7 @@
         <v>2002.9</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" s="26" t="s">
         <v>22</v>
       </c>
@@ -4665,7 +4497,7 @@
         <v>2710.5</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" s="26" t="s">
         <v>23</v>
       </c>
@@ -4673,7 +4505,7 @@
         <v>2234.5</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" s="26" t="s">
         <v>24</v>
       </c>
@@ -4681,7 +4513,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" s="26" t="s">
         <v>25</v>
       </c>
@@ -4689,7 +4521,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" s="26" t="s">
         <v>26</v>
       </c>
@@ -4697,7 +4529,7 @@
         <v>1979.1</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" s="26" t="s">
         <v>27</v>
       </c>
@@ -4705,7 +4537,7 @@
         <v>1898.7</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" s="26" t="s">
         <v>28</v>
       </c>
@@ -4713,15 +4545,15 @@
         <v>2215.6</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A33" s="26" t="s">
         <v>29</v>
       </c>
       <c r="B33" s="26">
-        <v>2234.3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
+        <v>2234.3000000000002</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A34" s="26" t="s">
         <v>30</v>
       </c>
@@ -4729,7 +4561,7 @@
         <v>2101.1</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A35" s="26" t="s">
         <v>31</v>
       </c>
@@ -4737,15 +4569,15 @@
         <v>1930.8</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A36" s="26" t="s">
         <v>32</v>
       </c>
       <c r="B36" s="26">
-        <v>2060.7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
+        <v>2060.6999999999998</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A37" s="26" t="s">
         <v>33</v>
       </c>
@@ -4753,7 +4585,7 @@
         <v>2122</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A38" s="26" t="s">
         <v>34</v>
       </c>
@@ -4761,7 +4593,7 @@
         <v>2151.4</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A39" s="26" t="s">
         <v>35</v>
       </c>
@@ -4769,7 +4601,7 @@
         <v>1987.8</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A40" s="26" t="s">
         <v>36</v>
       </c>
@@ -4777,31 +4609,31 @@
         <v>1869.8</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A41" s="26" t="s">
         <v>37</v>
       </c>
       <c r="B41" s="26">
-        <v>2209.3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
+        <v>2209.3000000000002</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A42" s="26" t="s">
         <v>38</v>
       </c>
       <c r="B42" s="26">
-        <v>2228.3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
+        <v>2228.3000000000002</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A43" s="26" t="s">
         <v>39</v>
       </c>
       <c r="B43" s="26">
-        <v>2075.8</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
+        <v>2075.8000000000002</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A44" s="26" t="s">
         <v>40</v>
       </c>
@@ -4809,7 +4641,7 @@
         <v>1830</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A45" s="26" t="s">
         <v>41</v>
       </c>
@@ -4817,7 +4649,7 @@
         <v>2002.5</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A46" s="26" t="s">
         <v>42</v>
       </c>
@@ -4825,7 +4657,7 @@
         <v>2038.7</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A47" s="26" t="s">
         <v>43</v>
       </c>
@@ -4833,15 +4665,15 @@
         <v>1852.9</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A48" s="26" t="s">
         <v>44</v>
       </c>
       <c r="B48" s="26">
-        <v>2288.2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
+        <v>2288.1999999999998</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A49" s="26" t="s">
         <v>45</v>
       </c>
@@ -4849,7 +4681,7 @@
         <v>1751.3</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A50" s="26" t="s">
         <v>46</v>
       </c>
@@ -4857,15 +4689,15 @@
         <v>1927</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A51" s="26" t="s">
         <v>47</v>
       </c>
       <c r="B51" s="26">
-        <v>2403.3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
+        <v>2403.3000000000002</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A52" s="26" t="s">
         <v>48</v>
       </c>
@@ -4873,7 +4705,7 @@
         <v>2550.1</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A53" s="26" t="s">
         <v>49</v>
       </c>
@@ -4881,7 +4713,7 @@
         <v>2357.5</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A54" s="26" t="s">
         <v>50</v>
       </c>
@@ -4889,15 +4721,15 @@
         <v>1896.1</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A55" s="26" t="s">
         <v>51</v>
       </c>
       <c r="B55" s="26">
-        <v>2066.7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
+        <v>2066.6999999999998</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A56" s="26" t="s">
         <v>52</v>
       </c>
@@ -4905,7 +4737,7 @@
         <v>1961.6</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A57" s="26" t="s">
         <v>53</v>
       </c>
@@ -4913,7 +4745,7 @@
         <v>2116.6</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A58" s="26" t="s">
         <v>54</v>
       </c>
@@ -4921,7 +4753,7 @@
         <v>2008.5</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A59" s="26" t="s">
         <v>55</v>
       </c>
@@ -4929,7 +4761,7 @@
         <v>2005.2</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A60" s="26" t="s">
         <v>56</v>
       </c>
@@ -4937,7 +4769,7 @@
         <v>2115</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A61" s="26" t="s">
         <v>57</v>
       </c>
@@ -4945,7 +4777,7 @@
         <v>2302.5</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A62" s="26" t="s">
         <v>58</v>
       </c>
@@ -4953,7 +4785,7 @@
         <v>2147.4</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A63" s="26" t="s">
         <v>59</v>
       </c>
@@ -4961,7 +4793,7 @@
         <v>1842.6</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A64" s="26" t="s">
         <v>60</v>
       </c>
@@ -4969,7 +4801,7 @@
         <v>1905.6</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A65" s="26" t="s">
         <v>61</v>
       </c>
@@ -4977,15 +4809,15 @@
         <v>1948.2</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A66" s="26" t="s">
         <v>62</v>
       </c>
       <c r="B66" s="26">
-        <v>2568.2</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
+        <v>2568.1999999999998</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A67" s="26" t="s">
         <v>63</v>
       </c>
@@ -4993,7 +4825,7 @@
         <v>1982.9</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A68" s="26" t="s">
         <v>64</v>
       </c>
@@ -5001,15 +4833,15 @@
         <v>1875.4</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A69" s="26" t="s">
         <v>65</v>
       </c>
       <c r="B69" s="26">
-        <v>2236.7</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
+        <v>2236.6999999999998</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A70" s="26" t="s">
         <v>66</v>
       </c>
@@ -5017,7 +4849,7 @@
         <v>2877.8</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A71" s="26" t="s">
         <v>67</v>
       </c>
@@ -5025,7 +4857,7 @@
         <v>2080.1</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A72" s="26" t="s">
         <v>68</v>
       </c>
@@ -5033,7 +4865,7 @@
         <v>2685.3</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A73" s="26" t="s">
         <v>69</v>
       </c>
@@ -5041,7 +4873,7 @@
         <v>1927.9</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A74" s="26" t="s">
         <v>70</v>
       </c>
@@ -5049,7 +4881,7 @@
         <v>2039</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A75" s="26" t="s">
         <v>71</v>
       </c>
@@ -5057,15 +4889,15 @@
         <v>2454.4</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A76" s="26" t="s">
         <v>72</v>
       </c>
       <c r="B76" s="26">
-        <v>2359.7</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2">
+        <v>2359.6999999999998</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A77" s="26" t="s">
         <v>73</v>
       </c>
@@ -5073,7 +4905,7 @@
         <v>2376.9</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A78" s="26" t="s">
         <v>74</v>
       </c>
@@ -5081,7 +4913,7 @@
         <v>2311.5</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A79" s="26" t="s">
         <v>75</v>
       </c>
@@ -5089,7 +4921,7 @@
         <v>2020.3</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A80" s="26" t="s">
         <v>76</v>
       </c>
@@ -5097,7 +4929,7 @@
         <v>2501.5</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A81" s="26" t="s">
         <v>77</v>
       </c>
@@ -5105,15 +4937,15 @@
         <v>2152.6</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A82" s="26" t="s">
         <v>78</v>
       </c>
       <c r="B82" s="26">
-        <v>2110.2</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2">
+        <v>2110.1999999999998</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A83" s="26" t="s">
         <v>79</v>
       </c>
@@ -5121,7 +4953,7 @@
         <v>1940.9</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A84" s="26" t="s">
         <v>80</v>
       </c>
@@ -5129,7 +4961,7 @@
         <v>2097.6</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A85" s="26" t="s">
         <v>81</v>
       </c>
@@ -5137,7 +4969,7 @@
         <v>2267.4</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A86" s="26" t="s">
         <v>82</v>
       </c>
@@ -5145,7 +4977,7 @@
         <v>2034.8</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A87" s="26" t="s">
         <v>83</v>
       </c>
@@ -5153,7 +4985,7 @@
         <v>2131.4</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A88" s="26" t="s">
         <v>84</v>
       </c>
@@ -5161,7 +4993,7 @@
         <v>3198.4</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A89" s="26" t="s">
         <v>85</v>
       </c>
@@ -5169,23 +5001,23 @@
         <v>2105.9</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A90" s="26" t="s">
         <v>86</v>
       </c>
       <c r="B90" s="26">
-        <v>2125.2</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2">
+        <v>2125.1999999999998</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A91" s="26" t="s">
         <v>87</v>
       </c>
       <c r="B91" s="26">
-        <v>2182.8</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2">
+        <v>2182.8000000000002</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A92" s="26" t="s">
         <v>88</v>
       </c>
@@ -5193,7 +5025,7 @@
         <v>2405.6</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A93" s="26" t="s">
         <v>89</v>
       </c>
@@ -5201,15 +5033,15 @@
         <v>2272.4</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A94" s="26" t="s">
         <v>90</v>
       </c>
       <c r="B94" s="26">
-        <v>2572.3</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2">
+        <v>2572.3000000000002</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A95" s="26" t="s">
         <v>91</v>
       </c>
@@ -5217,7 +5049,7 @@
         <v>3460.8</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A96" s="26" t="s">
         <v>92</v>
       </c>
@@ -5225,23 +5057,23 @@
         <v>2721</v>
       </c>
     </row>
-    <row r="97" spans="1:2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A97" s="26" t="s">
         <v>93</v>
       </c>
       <c r="B97" s="26">
-        <v>2127.3</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2">
+        <v>2127.3000000000002</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A98" s="26" t="s">
         <v>94</v>
       </c>
       <c r="B98" s="26">
-        <v>2409.7</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2">
+        <v>2409.6999999999998</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A99" s="26" t="s">
         <v>95</v>
       </c>
@@ -5249,7 +5081,7 @@
         <v>2149.9</v>
       </c>
     </row>
-    <row r="100" spans="1:2">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A100" s="26" t="s">
         <v>96</v>
       </c>
@@ -5257,7 +5089,7 @@
         <v>2254.1</v>
       </c>
     </row>
-    <row r="101" spans="1:2">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A101" s="26" t="s">
         <v>97</v>
       </c>
@@ -5265,15 +5097,15 @@
         <v>2941.2</v>
       </c>
     </row>
-    <row r="102" spans="1:2">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A102" s="26" t="s">
         <v>98</v>
       </c>
       <c r="B102" s="26">
-        <v>2198.7</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2">
+        <v>2198.6999999999998</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A103" s="26" t="s">
         <v>99</v>
       </c>
@@ -5281,7 +5113,7 @@
         <v>2308.1</v>
       </c>
     </row>
-    <row r="104" spans="1:2">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A104" s="26" t="s">
         <v>100</v>
       </c>
@@ -5289,15 +5121,15 @@
         <v>2240.4</v>
       </c>
     </row>
-    <row r="105" spans="1:2">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A105" s="26" t="s">
         <v>101</v>
       </c>
       <c r="B105" s="26">
-        <v>2579.7</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2">
+        <v>2579.6999999999998</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A106" s="26" t="s">
         <v>102</v>
       </c>
@@ -5305,7 +5137,7 @@
         <v>2459</v>
       </c>
     </row>
-    <row r="107" spans="1:2">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A107" s="26" t="s">
         <v>103</v>
       </c>
@@ -5313,15 +5145,15 @@
         <v>3309.5</v>
       </c>
     </row>
-    <row r="108" spans="1:2">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A108" s="26" t="s">
         <v>104</v>
       </c>
       <c r="B108" s="26">
-        <v>2303.8</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2">
+        <v>2303.8000000000002</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A109" s="26" t="s">
         <v>105</v>
       </c>
@@ -5329,7 +5161,7 @@
         <v>2215</v>
       </c>
     </row>
-    <row r="110" spans="1:2">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A110" s="26" t="s">
         <v>106</v>
       </c>
@@ -5337,23 +5169,23 @@
         <v>2606.1</v>
       </c>
     </row>
-    <row r="111" spans="1:2">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A111" s="26" t="s">
         <v>107</v>
       </c>
       <c r="B111" s="26">
-        <v>2567.3</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2">
+        <v>2567.3000000000002</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A112" s="26" t="s">
         <v>108</v>
       </c>
       <c r="B112" s="26">
-        <v>2401.7</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2">
+        <v>2401.6999999999998</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A113" s="26" t="s">
         <v>109</v>
       </c>
@@ -5361,7 +5193,7 @@
         <v>3083.5</v>
       </c>
     </row>
-    <row r="114" spans="1:2">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A114" s="26" t="s">
         <v>110</v>
       </c>
@@ -5369,7 +5201,7 @@
         <v>3220.8</v>
       </c>
     </row>
-    <row r="115" spans="1:2">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A115" s="26" t="s">
         <v>111</v>
       </c>
@@ -5377,7 +5209,7 @@
         <v>2257.6</v>
       </c>
     </row>
-    <row r="116" spans="1:2">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A116" s="26" t="s">
         <v>112</v>
       </c>
@@ -5385,15 +5217,15 @@
         <v>2361.6</v>
       </c>
     </row>
-    <row r="117" spans="1:2">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A117" s="26" t="s">
         <v>113</v>
       </c>
       <c r="B117" s="26">
-        <v>2384.7</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2">
+        <v>2384.6999999999998</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A118" s="26" t="s">
         <v>114</v>
       </c>
@@ -5401,7 +5233,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="119" ht="26.25" spans="1:2">
+    <row r="119" spans="1:2" ht="25.75" x14ac:dyDescent="0.4">
       <c r="A119" s="26" t="s">
         <v>115</v>
       </c>
@@ -5409,7 +5241,7 @@
         <v>2921.7</v>
       </c>
     </row>
-    <row r="120" spans="1:2">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A120" s="26" t="s">
         <v>116</v>
       </c>
@@ -5417,7 +5249,7 @@
         <v>2719.4</v>
       </c>
     </row>
-    <row r="121" spans="1:2">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A121" s="26" t="s">
         <v>117</v>
       </c>
@@ -5425,7 +5257,7 @@
         <v>2243.5</v>
       </c>
     </row>
-    <row r="122" spans="1:2">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A122" s="26" t="s">
         <v>118</v>
       </c>
@@ -5433,7 +5265,7 @@
         <v>2173.5</v>
       </c>
     </row>
-    <row r="123" spans="1:2">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A123" s="26" t="s">
         <v>119</v>
       </c>
@@ -5441,7 +5273,7 @@
         <v>1998.5</v>
       </c>
     </row>
-    <row r="124" spans="1:2">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A124" s="26" t="s">
         <v>120</v>
       </c>
@@ -5449,7 +5281,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="125" spans="1:2">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A125" s="26" t="s">
         <v>121</v>
       </c>
@@ -5457,7 +5289,7 @@
         <v>1952.4</v>
       </c>
     </row>
-    <row r="126" spans="1:2">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A126" s="26" t="s">
         <v>122</v>
       </c>
@@ -5465,7 +5297,7 @@
         <v>2102.5</v>
       </c>
     </row>
-    <row r="127" spans="1:2">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A127" s="26" t="s">
         <v>123</v>
       </c>
@@ -5473,7 +5305,7 @@
         <v>1891.5</v>
       </c>
     </row>
-    <row r="128" spans="1:2">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A128" s="26" t="s">
         <v>124</v>
       </c>
@@ -5481,7 +5313,7 @@
         <v>2018.8</v>
       </c>
     </row>
-    <row r="129" spans="1:2">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A129" s="26" t="s">
         <v>125</v>
       </c>
@@ -5489,7 +5321,7 @@
         <v>1953.3</v>
       </c>
     </row>
-    <row r="130" spans="1:2">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A130" s="26" t="s">
         <v>126</v>
       </c>
@@ -5497,15 +5329,15 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="131" spans="1:2">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A131" s="26" t="s">
         <v>127</v>
       </c>
       <c r="B131" s="26">
-        <v>2187.2</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2">
+        <v>2187.1999999999998</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A132" s="26" t="s">
         <v>128</v>
       </c>
@@ -5513,15 +5345,15 @@
         <v>1844.8</v>
       </c>
     </row>
-    <row r="133" spans="1:2">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A133" s="26" t="s">
         <v>129</v>
       </c>
       <c r="B133" s="26">
-        <v>2123.2</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2">
+        <v>2123.1999999999998</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A134" s="26" t="s">
         <v>130</v>
       </c>
@@ -5529,15 +5361,15 @@
         <v>1940.3</v>
       </c>
     </row>
-    <row r="135" spans="1:2">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A135" s="26" t="s">
         <v>131</v>
       </c>
       <c r="B135" s="26">
-        <v>2533.8</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2">
+        <v>2533.8000000000002</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A136" s="26" t="s">
         <v>132</v>
       </c>
@@ -5545,15 +5377,15 @@
         <v>1913.1</v>
       </c>
     </row>
-    <row r="137" spans="1:2">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A137" s="26" t="s">
         <v>133</v>
       </c>
       <c r="B137" s="26">
-        <v>2296.2</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2">
+        <v>2296.1999999999998</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A138" s="26" t="s">
         <v>134</v>
       </c>
@@ -5561,7 +5393,7 @@
         <v>1862.2</v>
       </c>
     </row>
-    <row r="139" spans="1:2">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A139" s="26" t="s">
         <v>135</v>
       </c>
@@ -5569,7 +5401,7 @@
         <v>1895.3</v>
       </c>
     </row>
-    <row r="140" spans="1:2">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A140" s="26" t="s">
         <v>136</v>
       </c>
@@ -5577,7 +5409,7 @@
         <v>1924.3</v>
       </c>
     </row>
-    <row r="141" spans="1:2">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A141" s="26" t="s">
         <v>137</v>
       </c>
@@ -5585,7 +5417,7 @@
         <v>1924.4</v>
       </c>
     </row>
-    <row r="142" spans="1:2">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A142" s="26" t="s">
         <v>138</v>
       </c>
@@ -5593,7 +5425,7 @@
         <v>2401</v>
       </c>
     </row>
-    <row r="143" spans="1:2">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A143" s="26" t="s">
         <v>139</v>
       </c>
@@ -5601,58 +5433,56 @@
         <v>2454.9</v>
       </c>
     </row>
-    <row r="144" spans="1:2">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A144" s="26" t="s">
         <v>140</v>
       </c>
       <c r="B144" s="26">
-        <v>2149.7</v>
+        <v>2149.6999999999998</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AD131"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="34.9203539823009" customWidth="1"/>
-    <col min="2" max="2" width="10.6106194690265" customWidth="1"/>
+    <col min="1" max="1" width="34.921875" customWidth="1"/>
+    <col min="2" max="2" width="10.61328125" customWidth="1"/>
     <col min="3" max="3" width="12" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.6106194690265" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.6106194690265" style="1" customWidth="1"/>
-    <col min="6" max="6" width="23.3008849557522" customWidth="1"/>
-    <col min="7" max="7" width="23.7699115044248" customWidth="1"/>
-    <col min="9" max="9" width="18.5309734513274" customWidth="1"/>
-    <col min="10" max="10" width="13.3805309734513" customWidth="1"/>
-    <col min="11" max="11" width="14.070796460177" customWidth="1"/>
-    <col min="12" max="12" width="12.8407079646018" customWidth="1"/>
+    <col min="4" max="4" width="14.61328125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.61328125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="23.3046875" customWidth="1"/>
+    <col min="7" max="7" width="23.765625" customWidth="1"/>
+    <col min="9" max="9" width="18.53515625" customWidth="1"/>
+    <col min="10" max="10" width="13.3828125" customWidth="1"/>
+    <col min="11" max="11" width="14.07421875" customWidth="1"/>
+    <col min="12" max="12" width="12.84375" customWidth="1"/>
     <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="14" width="15.2300884955752" customWidth="1"/>
-    <col min="15" max="15" width="10.7699115044248" customWidth="1"/>
-    <col min="16" max="16" width="11.8407079646018" customWidth="1"/>
-    <col min="17" max="17" width="14.2300884955752" customWidth="1"/>
-    <col min="18" max="18" width="15.2300884955752" customWidth="1"/>
-    <col min="19" max="19" width="3.76991150442478" customWidth="1"/>
-    <col min="20" max="20" width="23.5309734513274" customWidth="1"/>
-    <col min="21" max="21" width="11.8407079646018" customWidth="1"/>
-    <col min="23" max="23" width="10.4601769911504" customWidth="1"/>
+    <col min="14" max="14" width="15.23046875" customWidth="1"/>
+    <col min="15" max="15" width="10.765625" customWidth="1"/>
+    <col min="16" max="16" width="11.84375" customWidth="1"/>
+    <col min="17" max="17" width="14.23046875" customWidth="1"/>
+    <col min="18" max="18" width="15.23046875" customWidth="1"/>
+    <col min="19" max="19" width="3.765625" customWidth="1"/>
+    <col min="20" max="20" width="23.53515625" customWidth="1"/>
+    <col min="21" max="21" width="11.84375" customWidth="1"/>
+    <col min="23" max="23" width="10.4609375" customWidth="1"/>
     <col min="25" max="25" width="9" customWidth="1"/>
-    <col min="26" max="26" width="12.070796460177" customWidth="1"/>
-    <col min="27" max="27" width="11.8407079646018" customWidth="1"/>
-    <col min="28" max="28" width="11.9203539823009" customWidth="1"/>
-    <col min="29" max="29" width="12.6902654867257" customWidth="1"/>
-    <col min="30" max="30" width="14.5309734513274" customWidth="1"/>
+    <col min="26" max="26" width="12.07421875" customWidth="1"/>
+    <col min="27" max="27" width="11.84375" customWidth="1"/>
+    <col min="28" max="28" width="11.921875" customWidth="1"/>
+    <col min="29" max="29" width="12.69140625" customWidth="1"/>
+    <col min="30" max="30" width="14.53515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>141</v>
       </c>
@@ -5660,7 +5490,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="2" spans="1:27">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -5722,7 +5552,7 @@
       <c r="Z2" s="8"/>
       <c r="AA2" s="8"/>
     </row>
-    <row r="3" spans="1:27">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A3" s="5" t="s">
         <v>91</v>
       </c>
@@ -5735,10 +5565,10 @@
       </c>
       <c r="D3" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>8.14925505519879</v>
+        <v>8.149255055198795</v>
       </c>
       <c r="E3" s="6" t="str">
-        <f>IF(OR(C3&gt;3*$G$4,C3&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" ref="E3:E34" si="0">IF(OR(C3&gt;3*$G$4,C3&lt;$G$4/3),"ВЫБРОС","ОК")</f>
         <v>ОК</v>
       </c>
       <c r="F3" s="5" t="s">
@@ -5746,7 +5576,7 @@
       </c>
       <c r="G3" s="8">
         <f>AVERAGE(Таблица2[2025])</f>
-        <v>2225.06976744186</v>
+        <v>2225.0697674418602</v>
       </c>
       <c r="I3" s="5">
         <v>1</v>
@@ -5757,7 +5587,7 @@
       </c>
       <c r="K3" s="8">
         <f>J3+$G$15</f>
-        <v>1941.24444444444</v>
+        <v>1941.2444444444445</v>
       </c>
       <c r="L3" s="8">
         <f>ROUND((Таблица3[[#This Row],[Ниж. Гран]]+Таблица3[[#This Row],[Верх. Гран.]])/2,2)</f>
@@ -5769,38 +5599,38 @@
       </c>
       <c r="N3" s="12">
         <f>Таблица3[[#This Row],[Частота]]/$G$2</f>
-        <v>0.162790697674419</v>
+        <v>0.16279069767441862</v>
       </c>
       <c r="O3" s="8">
         <f>Таблица3[[#This Row],[Частота]]</f>
         <v>21</v>
       </c>
-      <c r="P3" s="8" t="e">
-        <f>LOGNORM.DIST(Таблица3[[#This Row],[Верх. Гран.]],$U$4,$U$5,TRUE)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="Q3" s="8" t="e">
+      <c r="P3" s="8">
+        <f>_xlfn.LOGNORM.DIST(Таблица3[[#This Row],[Верх. Гран.]],$U$4,$U$5,TRUE)</f>
+        <v>0.16110402062873369</v>
+      </c>
+      <c r="Q3" s="8">
         <f>Таблица3[[#This Row],[F(b_i)]]</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="R3" s="8" t="e">
+        <v>0.16110402062873369</v>
+      </c>
+      <c r="R3" s="8">
         <f>Таблица3[[#This Row],[тервер(р_i)]]*$G$2</f>
-        <v>#NAME?</v>
+        <v>20.782418661106647</v>
       </c>
       <c r="Y3" s="19">
         <f>M3</f>
         <v>21</v>
       </c>
-      <c r="Z3" s="19" t="e">
+      <c r="Z3" s="19">
         <f>R3</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="AA3" s="8" t="e">
+        <v>20.782418661106647</v>
+      </c>
+      <c r="AA3" s="8">
         <f>(Y3-Z3)*(Y3-Z3)/Z3</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27">
+        <v>2.2779658040101959E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A4" s="5" t="s">
         <v>103</v>
       </c>
@@ -5813,10 +5643,10 @@
       </c>
       <c r="D4" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>8.10455239955898</v>
+        <v>8.1045523995589779</v>
       </c>
       <c r="E4" s="6" t="str">
-        <f>IF(OR(C4&gt;3*$G$4,C4&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="0"/>
         <v>ОК</v>
       </c>
       <c r="F4" s="5" t="s">
@@ -5831,11 +5661,11 @@
       </c>
       <c r="J4" s="8">
         <f>K3</f>
-        <v>1941.24444444444</v>
+        <v>1941.2444444444445</v>
       </c>
       <c r="K4" s="8">
         <f>J4+$G$15</f>
-        <v>2131.18888888889</v>
+        <v>2131.1888888888889</v>
       </c>
       <c r="L4" s="8">
         <f>ROUND((Таблица3[[#This Row],[Ниж. Гран]]+Таблица3[[#This Row],[Верх. Гран.]])/2,2)</f>
@@ -5847,45 +5677,45 @@
       </c>
       <c r="N4" s="8">
         <f>Таблица3[[#This Row],[Частота]]/$G$2</f>
-        <v>0.286821705426357</v>
+        <v>0.2868217054263566</v>
       </c>
       <c r="O4" s="8">
         <f>O3+Таблица3[[#This Row],[Частота]]</f>
         <v>58</v>
       </c>
-      <c r="P4" s="8" t="e">
+      <c r="P4" s="8">
         <f>_xlfn.LOGNORM.DIST(Таблица3[[#This Row],[Верх. Гран.]],$U$4,$U$5,TRUE)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="Q4" s="8" t="e">
+        <v>0.39482735599611141</v>
+      </c>
+      <c r="Q4" s="8">
         <f>Таблица3[[#This Row],[F(b_i)]]-_xlfn.LOGNORM.DIST(Таблица3[[#This Row],[Ниж. Гран]],$U$4,$U$5,TRUE)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="R4" s="8" t="e">
+        <v>0.23372333536737772</v>
+      </c>
+      <c r="R4" s="8">
         <f>Таблица3[[#This Row],[тервер(р_i)]]*$G$2</f>
-        <v>#NAME?</v>
+        <v>30.150310262391724</v>
       </c>
       <c r="T4" s="8" t="s">
         <v>160</v>
       </c>
       <c r="U4" s="8">
         <f>AVERAGE(Таблица2[ln_2025])</f>
-        <v>7.69886990965716</v>
+        <v>7.6988699096571587</v>
       </c>
       <c r="Y4" s="19">
         <f>M4</f>
         <v>37</v>
       </c>
-      <c r="Z4" s="19" t="e">
+      <c r="Z4" s="19">
         <f>R4</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="AA4" s="8" t="e">
-        <f t="shared" ref="AA4:AA8" si="0">(Y4-Z4)*(Y4-Z4)/Z4</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27">
+        <v>30.150310262391724</v>
+      </c>
+      <c r="AA4" s="8">
+        <f t="shared" ref="AA4:AA8" si="1">(Y4-Z4)*(Y4-Z4)/Z4</f>
+        <v>1.5561448321153784</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A5" s="5" t="s">
         <v>110</v>
       </c>
@@ -5898,10 +5728,10 @@
       </c>
       <c r="D5" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>8.07738505488553</v>
+        <v>8.0773850548855268</v>
       </c>
       <c r="E5" s="6" t="str">
-        <f>IF(OR(C5&gt;3*$G$4,C5&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="0"/>
         <v>ОК</v>
       </c>
       <c r="F5" s="5" t="s">
@@ -5914,12 +5744,12 @@
         <v>3</v>
       </c>
       <c r="J5" s="8">
-        <f t="shared" ref="J5:J11" si="1">K4</f>
-        <v>2131.18888888889</v>
+        <f t="shared" ref="J5:J11" si="2">K4</f>
+        <v>2131.1888888888889</v>
       </c>
       <c r="K5" s="8">
-        <f t="shared" ref="K5:K11" si="2">J5+$G$15</f>
-        <v>2321.13333333333</v>
+        <f t="shared" ref="K5:K11" si="3">J5+$G$15</f>
+        <v>2321.1333333333332</v>
       </c>
       <c r="L5" s="8">
         <f>ROUND((Таблица3[[#This Row],[Ниж. Гран]]+Таблица3[[#This Row],[Верх. Гран.]])/2,2)</f>
@@ -5931,45 +5761,45 @@
       </c>
       <c r="N5" s="8">
         <f>Таблица3[[#This Row],[Частота]]/$G$2</f>
-        <v>0.294573643410853</v>
+        <v>0.29457364341085274</v>
       </c>
       <c r="O5" s="8">
         <f>O4+Таблица3[[#This Row],[Частота]]</f>
         <v>96</v>
       </c>
-      <c r="P5" s="8" t="e">
+      <c r="P5" s="8">
         <f>_xlfn.LOGNORM.DIST(Таблица3[[#This Row],[Верх. Гран.]],$U$4,$U$5,TRUE)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="Q5" s="8" t="e">
+        <v>0.65344214655868083</v>
+      </c>
+      <c r="Q5" s="8">
         <f>Таблица3[[#This Row],[F(b_i)]]-_xlfn.LOGNORM.DIST(Таблица3[[#This Row],[Ниж. Гран]],$U$4,$U$5,TRUE)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="R5" s="8" t="e">
+        <v>0.25861479056256942</v>
+      </c>
+      <c r="R5" s="8">
         <f>Таблица3[[#This Row],[тервер(р_i)]]*$G$2</f>
-        <v>#NAME?</v>
+        <v>33.361307982571454</v>
       </c>
       <c r="T5" s="8" t="s">
         <v>163</v>
       </c>
       <c r="U5" s="8">
         <f>_xlfn.STDEV.S(Таблица2[ln_2025])</f>
-        <v>0.129085207549801</v>
+        <v>0.12908520754980041</v>
       </c>
       <c r="Y5" s="19">
         <f>M5</f>
         <v>38</v>
       </c>
-      <c r="Z5" s="19" t="e">
+      <c r="Z5" s="19">
         <f>R5</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="AA5" s="8" t="e">
-        <f t="shared" si="0"/>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27">
+        <v>33.361307982571454</v>
+      </c>
+      <c r="AA5" s="8">
+        <f t="shared" si="1"/>
+        <v>0.64498261410483149</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A6" s="5" t="s">
         <v>84</v>
       </c>
@@ -5982,10 +5812,10 @@
       </c>
       <c r="D6" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>8.07040596374614</v>
+        <v>8.0704059637461363</v>
       </c>
       <c r="E6" s="6" t="str">
-        <f>IF(OR(C6&gt;3*$G$4,C6&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="0"/>
         <v>ОК</v>
       </c>
       <c r="F6" s="5" t="s">
@@ -5993,18 +5823,18 @@
       </c>
       <c r="G6" s="8">
         <f>_xlfn.VAR.S(Таблица2[2025])</f>
-        <v>96264.7949382272</v>
+        <v>96264.794938227162</v>
       </c>
       <c r="I6" s="5">
         <v>4</v>
       </c>
       <c r="J6" s="8">
-        <f t="shared" si="1"/>
-        <v>2321.13333333333</v>
+        <f t="shared" si="2"/>
+        <v>2321.1333333333332</v>
       </c>
       <c r="K6" s="8">
-        <f t="shared" si="2"/>
-        <v>2511.07777777778</v>
+        <f t="shared" si="3"/>
+        <v>2511.0777777777776</v>
       </c>
       <c r="L6" s="8">
         <f>ROUND((Таблица3[[#This Row],[Ниж. Гран]]+Таблица3[[#This Row],[Верх. Гран.]])/2,2)</f>
@@ -6016,38 +5846,38 @@
       </c>
       <c r="N6" s="8">
         <f>Таблица3[[#This Row],[Частота]]/$G$2</f>
-        <v>0.124031007751938</v>
+        <v>0.12403100775193798</v>
       </c>
       <c r="O6" s="8">
         <f>O5+Таблица3[[#This Row],[Частота]]</f>
         <v>112</v>
       </c>
-      <c r="P6" s="8" t="e">
+      <c r="P6" s="8">
         <f>_xlfn.LOGNORM.DIST(Таблица3[[#This Row],[Верх. Гран.]],$U$4,$U$5,TRUE)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="Q6" s="8" t="e">
+        <v>0.84230299254674068</v>
+      </c>
+      <c r="Q6" s="8">
         <f>Таблица3[[#This Row],[F(b_i)]]-_xlfn.LOGNORM.DIST(Таблица3[[#This Row],[Ниж. Гран]],$U$4,$U$5,TRUE)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="R6" s="8" t="e">
+        <v>0.18886084598805986</v>
+      </c>
+      <c r="R6" s="8">
         <f>Таблица3[[#This Row],[тервер(р_i)]]*$G$2</f>
-        <v>#NAME?</v>
+        <v>24.363049132459722</v>
       </c>
       <c r="Y6" s="19">
         <f>M6</f>
         <v>16</v>
       </c>
-      <c r="Z6" s="19" t="e">
+      <c r="Z6" s="19">
         <f>R6</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="AA6" s="8" t="e">
-        <f t="shared" si="0"/>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27">
+        <v>24.363049132459722</v>
+      </c>
+      <c r="AA6" s="8">
+        <f t="shared" si="1"/>
+        <v>2.8707650841105545</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A7" s="5" t="s">
         <v>109</v>
       </c>
@@ -6060,10 +5890,10 @@
       </c>
       <c r="D7" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>8.03382059443155</v>
+        <v>8.0338205944315479</v>
       </c>
       <c r="E7" s="6" t="str">
-        <f>IF(OR(C7&gt;3*$G$4,C7&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="0"/>
         <v>ОК</v>
       </c>
       <c r="F7" s="5" t="s">
@@ -6071,22 +5901,22 @@
       </c>
       <c r="G7" s="8">
         <f>SQRT(G6)</f>
-        <v>310.265684435497</v>
+        <v>310.26568443549661</v>
       </c>
       <c r="I7" s="5">
         <v>5</v>
       </c>
       <c r="J7" s="8">
-        <f t="shared" si="1"/>
-        <v>2511.07777777778</v>
+        <f t="shared" si="2"/>
+        <v>2511.0777777777776</v>
       </c>
       <c r="K7" s="8">
-        <f t="shared" si="2"/>
-        <v>2701.02222222222</v>
+        <f t="shared" si="3"/>
+        <v>2701.0222222222219</v>
       </c>
       <c r="L7" s="8">
         <f>ROUND((Таблица3[[#This Row],[Ниж. Гран]]+Таблица3[[#This Row],[Верх. Гран.]])/2,2)</f>
-        <v>2606.05</v>
+        <v>2606.0500000000002</v>
       </c>
       <c r="M7" s="16">
         <f>IF(Таблица3[[#This Row],[Интервал]]=MAX(Таблица3[Интервал]),COUNTIFS(Таблица2[2025],"&gt;="&amp;Таблица3[[#This Row],[Ниж. Гран]],Таблица2[2025],"&lt;="&amp;Таблица3[[#This Row],[Верх. Гран.]]),COUNTIFS(Таблица2[2025],"&gt;="&amp;Таблица3[[#This Row],[Ниж. Гран]],Таблица2[2025],"&lt;"&amp;Таблица3[[#This Row],[Верх. Гран.]]))</f>
@@ -6094,38 +5924,38 @@
       </c>
       <c r="N7" s="8">
         <f>Таблица3[[#This Row],[Частота]]/$G$2</f>
-        <v>0.062015503875969</v>
+        <v>6.2015503875968991E-2</v>
       </c>
       <c r="O7" s="8">
         <f>O6+Таблица3[[#This Row],[Частота]]</f>
         <v>120</v>
       </c>
-      <c r="P7" s="8" t="e">
+      <c r="P7" s="8">
         <f>_xlfn.LOGNORM.DIST(Таблица3[[#This Row],[Верх. Гран.]],$U$4,$U$5,TRUE)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="Q7" s="8" t="e">
+        <v>0.94165886287483791</v>
+      </c>
+      <c r="Q7" s="8">
         <f>Таблица3[[#This Row],[F(b_i)]]-_xlfn.LOGNORM.DIST(Таблица3[[#This Row],[Ниж. Гран]],$U$4,$U$5,TRUE)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="R7" s="8" t="e">
+        <v>9.9355870328097229E-2</v>
+      </c>
+      <c r="R7" s="8">
         <f>Таблица3[[#This Row],[тервер(р_i)]]*$G$2</f>
-        <v>#NAME?</v>
+        <v>12.816907272324542</v>
       </c>
       <c r="Y7" s="19">
         <f>M7</f>
         <v>8</v>
       </c>
-      <c r="Z7" s="19" t="e">
+      <c r="Z7" s="19">
         <f>R7</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="AA7" s="8" t="e">
-        <f t="shared" si="0"/>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27">
+        <v>12.816907272324542</v>
+      </c>
+      <c r="AA7" s="8">
+        <f t="shared" si="1"/>
+        <v>1.8103115811935584</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A8" s="5" t="s">
         <v>97</v>
       </c>
@@ -6138,10 +5968,10 @@
       </c>
       <c r="D8" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.98657294032207</v>
+        <v>7.9865729403220671</v>
       </c>
       <c r="E8" s="6" t="str">
-        <f>IF(OR(C8&gt;3*$G$4,C8&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="0"/>
         <v>ОК</v>
       </c>
       <c r="F8" s="5" t="s">
@@ -6149,18 +5979,18 @@
       </c>
       <c r="G8" s="8">
         <f>G7/G3*100</f>
-        <v>13.9440879102054</v>
+        <v>13.944087910205436</v>
       </c>
       <c r="I8" s="5">
         <v>6</v>
       </c>
       <c r="J8" s="8">
-        <f t="shared" si="1"/>
-        <v>2701.02222222222</v>
+        <f t="shared" si="2"/>
+        <v>2701.0222222222219</v>
       </c>
       <c r="K8" s="8">
-        <f t="shared" si="2"/>
-        <v>2890.96666666667</v>
+        <f t="shared" si="3"/>
+        <v>2890.9666666666662</v>
       </c>
       <c r="L8" s="8">
         <f>ROUND((Таблица3[[#This Row],[Ниж. Гран]]+Таблица3[[#This Row],[Верх. Гран.]])/2,2)</f>
@@ -6172,23 +6002,23 @@
       </c>
       <c r="N8" s="8">
         <f>Таблица3[[#This Row],[Частота]]/$G$2</f>
-        <v>0.0232558139534884</v>
+        <v>2.3255813953488372E-2</v>
       </c>
       <c r="O8" s="8">
         <f>O7+Таблица3[[#This Row],[Частота]]</f>
         <v>123</v>
       </c>
-      <c r="P8" s="8" t="e">
+      <c r="P8" s="8">
         <f>_xlfn.LOGNORM.DIST(Таблица3[[#This Row],[Верх. Гран.]],$U$4,$U$5,TRUE)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="Q8" s="8" t="e">
+        <v>0.98192923316342662</v>
+      </c>
+      <c r="Q8" s="8">
         <f>Таблица3[[#This Row],[F(b_i)]]-_xlfn.LOGNORM.DIST(Таблица3[[#This Row],[Ниж. Гран]],$U$4,$U$5,TRUE)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="R8" s="8" t="e">
+        <v>4.0270370288588708E-2</v>
+      </c>
+      <c r="R8" s="8">
         <f>Таблица3[[#This Row],[тервер(р_i)]]*$G$2</f>
-        <v>#NAME?</v>
+        <v>5.1948777672279434</v>
       </c>
       <c r="S8" t="s">
         <v>167</v>
@@ -6197,16 +6027,16 @@
         <f>SUM(M8:M11)</f>
         <v>9</v>
       </c>
-      <c r="Z8" s="19" t="e">
+      <c r="Z8" s="19">
         <f>SUM(R8:R11)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="AA8" s="8" t="e">
-        <f t="shared" si="0"/>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18">
+        <v>7.5260066891459099</v>
+      </c>
+      <c r="AA8" s="8">
+        <f t="shared" si="1"/>
+        <v>0.28868646683187665</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A9" s="5" t="s">
         <v>66</v>
       </c>
@@ -6219,10 +6049,10 @@
       </c>
       <c r="D9" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.96478139232932</v>
+        <v>7.9647813923293169</v>
       </c>
       <c r="E9" s="6" t="str">
-        <f>IF(OR(C9&gt;3*$G$4,C9&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="0"/>
         <v>ОК</v>
       </c>
       <c r="F9" s="9" t="s">
@@ -6236,12 +6066,12 @@
         <v>7</v>
       </c>
       <c r="J9" s="8">
-        <f t="shared" si="1"/>
-        <v>2890.96666666667</v>
+        <f t="shared" si="2"/>
+        <v>2890.9666666666662</v>
       </c>
       <c r="K9" s="8">
-        <f t="shared" si="2"/>
-        <v>3080.91111111111</v>
+        <f t="shared" si="3"/>
+        <v>3080.9111111111106</v>
       </c>
       <c r="L9" s="8">
         <f>ROUND((Таблица3[[#This Row],[Ниж. Гран]]+Таблица3[[#This Row],[Верх. Гран.]])/2,2)</f>
@@ -6253,26 +6083,26 @@
       </c>
       <c r="N9" s="8">
         <f>Таблица3[[#This Row],[Частота]]/$G$2</f>
-        <v>0.00775193798449612</v>
+        <v>7.7519379844961239E-3</v>
       </c>
       <c r="O9" s="8">
         <f>O8+Таблица3[[#This Row],[Частота]]</f>
         <v>124</v>
       </c>
-      <c r="P9" s="8" t="e">
+      <c r="P9" s="8">
         <f>_xlfn.LOGNORM.DIST(Таблица3[[#This Row],[Верх. Гран.]],$U$4,$U$5,TRUE)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="Q9" s="8" t="e">
+        <v>0.99517739830445739</v>
+      </c>
+      <c r="Q9" s="8">
         <f>Таблица3[[#This Row],[F(b_i)]]-_xlfn.LOGNORM.DIST(Таблица3[[#This Row],[Ниж. Гран]],$U$4,$U$5,TRUE)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="R9" s="8" t="e">
+        <v>1.3248165141030777E-2</v>
+      </c>
+      <c r="R9" s="8">
         <f>Таблица3[[#This Row],[тервер(р_i)]]*$G$2</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26">
+        <v>1.7090133031929702</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A10" s="5" t="s">
         <v>116</v>
       </c>
@@ -6285,10 +6115,10 @@
       </c>
       <c r="D10" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.90816654672159</v>
+        <v>7.9081665467215858</v>
       </c>
       <c r="E10" s="6" t="str">
-        <f>IF(OR(C10&gt;3*$G$4,C10&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="0"/>
         <v>ОК</v>
       </c>
       <c r="F10" s="11" t="s">
@@ -6298,12 +6128,12 @@
         <v>8</v>
       </c>
       <c r="J10" s="8">
-        <f t="shared" si="1"/>
-        <v>3080.91111111111</v>
+        <f t="shared" si="2"/>
+        <v>3080.9111111111106</v>
       </c>
       <c r="K10" s="8">
-        <f t="shared" si="2"/>
-        <v>3270.85555555555</v>
+        <f t="shared" si="3"/>
+        <v>3270.8555555555549</v>
       </c>
       <c r="L10" s="8">
         <f>ROUND((Таблица3[[#This Row],[Ниж. Гран]]+Таблица3[[#This Row],[Верх. Гран.]])/2,2)</f>
@@ -6315,33 +6145,33 @@
       </c>
       <c r="N10" s="8">
         <f>Таблица3[[#This Row],[Частота]]/$G$2</f>
-        <v>0.0232558139534884</v>
+        <v>2.3255813953488372E-2</v>
       </c>
       <c r="O10" s="8">
         <f>O9+Таблица3[[#This Row],[Частота]]</f>
         <v>127</v>
       </c>
-      <c r="P10" s="8" t="e">
+      <c r="P10" s="8">
         <f>_xlfn.LOGNORM.DIST(Таблица3[[#This Row],[Верх. Гран.]],$U$4,$U$5,TRUE)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="Q10" s="8" t="e">
+        <v>0.99886247700067377</v>
+      </c>
+      <c r="Q10" s="8">
         <f>Таблица3[[#This Row],[F(b_i)]]-_xlfn.LOGNORM.DIST(Таблица3[[#This Row],[Ниж. Гран]],$U$4,$U$5,TRUE)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="R10" s="8" t="e">
+        <v>3.6850786962163706E-3</v>
+      </c>
+      <c r="R10" s="8">
         <f>Таблица3[[#This Row],[тервер(р_i)]]*$G$2</f>
-        <v>#NAME?</v>
+        <v>0.47537515181191181</v>
       </c>
       <c r="Y10" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="Z10" s="8" t="e">
+      <c r="Z10" s="8">
         <f>SUM(AA3:AA8)</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26">
+        <v>7.1731685441602098</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A11" s="5" t="s">
         <v>22</v>
       </c>
@@ -6354,22 +6184,22 @@
       </c>
       <c r="D11" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.90488839870039</v>
+        <v>7.9048883987003933</v>
       </c>
       <c r="E11" s="6" t="str">
-        <f>IF(OR(C11&gt;3*$G$4,C11&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="0"/>
         <v>ОК</v>
       </c>
       <c r="I11" s="13">
         <v>9</v>
       </c>
       <c r="J11" s="14">
-        <f t="shared" si="1"/>
-        <v>3270.85555555555</v>
+        <f t="shared" si="2"/>
+        <v>3270.8555555555549</v>
       </c>
       <c r="K11" s="14">
-        <f t="shared" si="2"/>
-        <v>3460.8</v>
+        <f t="shared" si="3"/>
+        <v>3460.7999999999993</v>
       </c>
       <c r="L11" s="14">
         <f>ROUND((Таблица3[[#This Row],[Ниж. Гран]]+Таблица3[[#This Row],[Верх. Гран.]])/2,2)</f>
@@ -6381,33 +6211,33 @@
       </c>
       <c r="N11" s="14">
         <f>Таблица3[[#This Row],[Частота]]/$G$2</f>
-        <v>0.0155038759689922</v>
+        <v>1.5503875968992248E-2</v>
       </c>
       <c r="O11" s="8">
         <f>O10+Таблица3[[#This Row],[Частота]]</f>
         <v>129</v>
       </c>
-      <c r="P11" s="8" t="e">
+      <c r="P11" s="8">
         <f>_xlfn.LOGNORM.DIST(Таблица3[[#This Row],[Верх. Гран.]],$U$4,$U$5,TRUE)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="Q11" s="8" t="e">
+        <v>0.99975763259035355</v>
+      </c>
+      <c r="Q11" s="8">
         <f>1-_xlfn.LOGNORM.DIST(Таблица3[[#This Row],[Ниж. Гран]],$U$4,$U$5,TRUE)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="R11" s="8" t="e">
+        <v>1.1375229993262348E-3</v>
+      </c>
+      <c r="R11" s="8">
         <f>Таблица3[[#This Row],[тервер(р_i)]]*$G$2</f>
-        <v>#NAME?</v>
+        <v>0.14674046691308429</v>
       </c>
       <c r="Y11" s="8" t="s">
         <v>171</v>
       </c>
       <c r="Z11" s="8">
         <f>COUNT(AA3:AA8)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A12" s="5" t="s">
         <v>68</v>
       </c>
@@ -6420,10 +6250,10 @@
       </c>
       <c r="D12" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.895547732545</v>
+        <v>7.895547732545003</v>
       </c>
       <c r="E12" s="6" t="str">
-        <f>IF(OR(C12&gt;3*$G$4,C12&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="0"/>
         <v>ОК</v>
       </c>
       <c r="F12" s="8" t="s">
@@ -6442,11 +6272,11 @@
       </c>
       <c r="K12" s="14">
         <f>SUBTOTAL(109,Таблица3[Верх. Гран.])</f>
-        <v>24309.2</v>
+        <v>24309.199999999997</v>
       </c>
       <c r="L12" s="14">
         <f>SUBTOTAL(109,Таблица3[Середина])</f>
-        <v>23454.45</v>
+        <v>23454.450000000004</v>
       </c>
       <c r="M12" s="14">
         <f>SUBTOTAL(109,Таблица3[Частота])</f>
@@ -6465,7 +6295,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A13" s="5" t="s">
         <v>106</v>
       </c>
@@ -6478,10 +6308,10 @@
       </c>
       <c r="D13" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.86561012993398</v>
+        <v>7.8656101299339847</v>
       </c>
       <c r="E13" s="6" t="str">
-        <f>IF(OR(C13&gt;3*$G$4,C13&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="0"/>
         <v>ОК</v>
       </c>
       <c r="F13" s="8" t="s">
@@ -6496,10 +6326,10 @@
       </c>
       <c r="Z13" s="8">
         <f>Z11-1-Z12</f>
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A14" s="5" t="s">
         <v>101</v>
       </c>
@@ -6508,14 +6338,14 @@
         <v>5</v>
       </c>
       <c r="C14" s="6">
-        <v>2579.7</v>
+        <v>2579.6999999999998</v>
       </c>
       <c r="D14" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.85542839208496</v>
+        <v>7.8554283920849608</v>
       </c>
       <c r="E14" s="6" t="str">
-        <f>IF(OR(C14&gt;3*$G$4,C14&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="0"/>
         <v>ОК</v>
       </c>
       <c r="F14" s="8" t="s">
@@ -6532,7 +6362,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="15" spans="1:27">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A15" s="5" t="s">
         <v>90</v>
       </c>
@@ -6541,14 +6371,14 @@
         <v>5</v>
       </c>
       <c r="C15" s="6">
-        <v>2572.3</v>
+        <v>2572.3000000000002</v>
       </c>
       <c r="D15" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.85255571930201</v>
+        <v>7.8525557193020079</v>
       </c>
       <c r="E15" s="6" t="str">
-        <f>IF(OR(C15&gt;3*$G$4,C15&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="0"/>
         <v>ОК</v>
       </c>
       <c r="F15" s="8" t="s">
@@ -6556,20 +6386,20 @@
       </c>
       <c r="G15" s="8">
         <f>(G14-G13)/G12</f>
-        <v>189.944444444444</v>
+        <v>189.94444444444446</v>
       </c>
       <c r="Y15" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="Z15" s="8" t="e">
+      <c r="Z15" s="8">
         <f>CHIINV(Z14,Z13)</f>
-        <v>#NUM!</v>
+        <v>7.8147279032511792</v>
       </c>
       <c r="AA15" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="16" spans="1:27">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.4">
       <c r="A16" s="5" t="s">
         <v>62</v>
       </c>
@@ -6578,28 +6408,28 @@
         <v>5</v>
       </c>
       <c r="C16" s="6">
-        <v>2568.2</v>
+        <v>2568.1999999999998</v>
       </c>
       <c r="D16" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.85096054339717</v>
+        <v>7.8509605433971732</v>
       </c>
       <c r="E16" s="6" t="str">
-        <f>IF(OR(C16&gt;3*$G$4,C16&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="0"/>
         <v>ОК</v>
       </c>
       <c r="Y16" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="Z16" s="8" t="e">
+      <c r="Z16" s="8">
         <f>CHIDIST(Z10,Z13)</f>
-        <v>#NAME?</v>
+        <v>6.6578405033844032E-2</v>
       </c>
       <c r="AA16" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="17" spans="1:26">
+    <row r="17" spans="1:30" x14ac:dyDescent="0.4">
       <c r="A17" s="5" t="s">
         <v>107</v>
       </c>
@@ -6608,14 +6438,14 @@
         <v>5</v>
       </c>
       <c r="C17" s="6">
-        <v>2567.3</v>
+        <v>2567.3000000000002</v>
       </c>
       <c r="D17" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.85061004198184</v>
+        <v>7.8506100419818434</v>
       </c>
       <c r="E17" s="6" t="str">
-        <f>IF(OR(C17&gt;3*$G$4,C17&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="0"/>
         <v>ОК</v>
       </c>
       <c r="Y17" s="20" t="s">
@@ -6625,7 +6455,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.4">
       <c r="A18" s="5" t="s">
         <v>48</v>
       </c>
@@ -6638,14 +6468,14 @@
       </c>
       <c r="D18" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.84388785306983</v>
+        <v>7.8438878530698313</v>
       </c>
       <c r="E18" s="6" t="str">
-        <f>IF(OR(C18&gt;3*$G$4,C18&lt;$G$4/3),"ВЫБРОС","ОК")</f>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <f t="shared" si="0"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.4">
       <c r="A19" s="5" t="s">
         <v>131</v>
       </c>
@@ -6654,18 +6484,18 @@
         <v>5</v>
       </c>
       <c r="C19" s="6">
-        <v>2533.8</v>
+        <v>2533.8000000000002</v>
       </c>
       <c r="D19" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.83747543116795</v>
+        <v>7.8374754311679533</v>
       </c>
       <c r="E19" s="6" t="str">
-        <f>IF(OR(C19&gt;3*$G$4,C19&lt;$G$4/3),"ВЫБРОС","ОК")</f>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="20" spans="1:30">
+        <f t="shared" si="0"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30" x14ac:dyDescent="0.4">
       <c r="A20" s="5" t="s">
         <v>8</v>
       </c>
@@ -6678,10 +6508,10 @@
       </c>
       <c r="D20" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.82484569102686</v>
+        <v>7.824845691026856</v>
       </c>
       <c r="E20" s="6" t="str">
-        <f>IF(OR(C20&gt;3*$G$4,C20&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="0"/>
         <v>ОК</v>
       </c>
       <c r="Y20" s="2" t="s">
@@ -6703,7 +6533,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="21" spans="1:30">
+    <row r="21" spans="1:30" x14ac:dyDescent="0.4">
       <c r="A21" s="5" t="s">
         <v>76</v>
       </c>
@@ -6716,10 +6546,10 @@
       </c>
       <c r="D21" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.82464583092826</v>
+        <v>7.8246458309282598</v>
       </c>
       <c r="E21" s="6" t="str">
-        <f>IF(OR(C21&gt;3*$G$4,C21&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="0"/>
         <v>ОК</v>
       </c>
       <c r="Y21" s="5">
@@ -6731,22 +6561,22 @@
       </c>
       <c r="AA21" s="8">
         <f>AVERAGEIF(Таблица2[Группа],Таблица1[[#This Row],[группа]],Таблица2[2025])</f>
-        <v>1887.85238095238</v>
-      </c>
-      <c r="AB21" s="8">
-        <f>_xlfn.VAR.P(_xlfn._xlws.FILTER(Таблица2[2025],Таблица2[Группа]=Таблица1[[#This Row],[группа]]))</f>
-        <v>2032.00439909297</v>
+        <v>1887.8523809523811</v>
+      </c>
+      <c r="AB21" s="8" cm="1">
+        <f t="array" ref="AB21">_xlfn.VAR.P(_xlfn._xlws.FILTER(Таблица2[2025],Таблица2[Группа]=Таблица1[[#This Row],[группа]]))</f>
+        <v>2032.0043990929712</v>
       </c>
       <c r="AC21" s="8">
         <f>Таблица1[[#This Row],[частота]]*Таблица1[[#This Row],[групп дисп]]</f>
-        <v>42672.0923809524</v>
+        <v>42672.092380952396</v>
       </c>
       <c r="AD21" s="16">
         <f>Таблица1[[#This Row],[частота]]*(Таблица1[[#This Row],[групп сред]]-$G$3)^2</f>
-        <v>2388026.88076671</v>
-      </c>
-    </row>
-    <row r="22" spans="1:30">
+        <v>2388026.8807666898</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" x14ac:dyDescent="0.4">
       <c r="A22" s="5" t="s">
         <v>102</v>
       </c>
@@ -6759,37 +6589,37 @@
       </c>
       <c r="D22" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.80751004221619</v>
+        <v>7.8075100422161929</v>
       </c>
       <c r="E22" s="6" t="str">
-        <f>IF(OR(C22&gt;3*$G$4,C22&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="0"/>
         <v>ОК</v>
       </c>
       <c r="Y22" s="5">
         <v>2</v>
       </c>
       <c r="Z22" s="8">
-        <f t="shared" ref="Z22:Z29" si="3">M4</f>
+        <f t="shared" ref="Z22:Z29" si="4">M4</f>
         <v>37</v>
       </c>
       <c r="AA22" s="8">
         <f>AVERAGEIF(Таблица2[Группа],Таблица1[[#This Row],[группа]],Таблица2[2025])</f>
-        <v>2048.7972972973</v>
-      </c>
-      <c r="AB22" s="8">
-        <f>_xlfn.VAR.P(_xlfn._xlws.FILTER(Таблица2[2025],Таблица2[Группа]=Таблица1[[#This Row],[группа]]))</f>
-        <v>3448.88566837107</v>
+        <v>2048.7972972972975</v>
+      </c>
+      <c r="AB22" s="8" cm="1">
+        <f t="array" ref="AB22">_xlfn.VAR.P(_xlfn._xlws.FILTER(Таблица2[2025],Таблица2[Группа]=Таблица1[[#This Row],[группа]]))</f>
+        <v>3448.8856683710719</v>
       </c>
       <c r="AC22" s="8">
         <f>Таблица1[[#This Row],[частота]]*Таблица1[[#This Row],[групп дисп]]</f>
-        <v>127608.76972973</v>
+        <v>127608.76972972965</v>
       </c>
       <c r="AD22" s="16">
         <f>Таблица1[[#This Row],[частота]]*(Таблица1[[#This Row],[групп сред]]-$G$3)^2</f>
-        <v>1149663.39804203</v>
-      </c>
-    </row>
-    <row r="23" spans="1:30">
+        <v>1149663.3980420327</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30" x14ac:dyDescent="0.4">
       <c r="A23" s="5" t="s">
         <v>139</v>
       </c>
@@ -6802,37 +6632,37 @@
       </c>
       <c r="D23" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.80584130620145</v>
+        <v>7.8058413062014456</v>
       </c>
       <c r="E23" s="6" t="str">
-        <f>IF(OR(C23&gt;3*$G$4,C23&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="0"/>
         <v>ОК</v>
       </c>
       <c r="Y23" s="5">
         <v>3</v>
       </c>
       <c r="Z23" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>38</v>
       </c>
       <c r="AA23" s="8">
         <f>AVERAGEIF(Таблица2[Группа],Таблица1[[#This Row],[группа]],Таблица2[2025])</f>
-        <v>2226.66578947368</v>
-      </c>
-      <c r="AB23" s="8">
+        <v>2226.6657894736841</v>
+      </c>
+      <c r="AB23" s="8" cm="1">
         <f t="array" ref="AB23">_xlfn.VAR.P(_xlfn._xlws.FILTER(Таблица2[2025],Таблица2[Группа]=Таблица1[[#This Row],[группа]]))</f>
-        <v>3088.61067174515</v>
+        <v>3088.6106717451507</v>
       </c>
       <c r="AC23" s="8">
         <f>Таблица1[[#This Row],[частота]]*Таблица1[[#This Row],[групп дисп]]</f>
-        <v>117367.205526316</v>
+        <v>117367.20552631572</v>
       </c>
       <c r="AD23" s="16">
         <f>Таблица1[[#This Row],[частота]]*(Таблица1[[#This Row],[групп сред]]-$G$3)^2</f>
-        <v>96.7968803905509</v>
-      </c>
-    </row>
-    <row r="24" spans="1:30">
+        <v>96.796880390550939</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" x14ac:dyDescent="0.4">
       <c r="A24" s="5" t="s">
         <v>71</v>
       </c>
@@ -6845,37 +6675,37 @@
       </c>
       <c r="D24" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.80563761117294</v>
+        <v>7.8056376111729371</v>
       </c>
       <c r="E24" s="6" t="str">
-        <f>IF(OR(C24&gt;3*$G$4,C24&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="0"/>
         <v>ОК</v>
       </c>
       <c r="Y24" s="5">
         <v>4</v>
       </c>
       <c r="Z24" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
       <c r="AA24" s="8">
         <f>AVERAGEIF(Таблица2[Группа],Таблица1[[#This Row],[группа]],Таблица2[2025])</f>
         <v>2424.1</v>
       </c>
-      <c r="AB24" s="8">
+      <c r="AB24" s="8" cm="1">
         <f t="array" ref="AB24">_xlfn.VAR.P(_xlfn._xlws.FILTER(Таблица2[2025],Таблица2[Группа]=Таблица1[[#This Row],[группа]]))</f>
-        <v>1614.29</v>
+        <v>1614.2900000000018</v>
       </c>
       <c r="AC24" s="8">
         <f>Таблица1[[#This Row],[частота]]*Таблица1[[#This Row],[групп дисп]]</f>
-        <v>25828.64</v>
+        <v>25828.640000000029</v>
       </c>
       <c r="AD24" s="16">
         <f>Таблица1[[#This Row],[частота]]*(Таблица1[[#This Row],[групп сред]]-$G$3)^2</f>
-        <v>633808.535554355</v>
-      </c>
-    </row>
-    <row r="25" spans="1:30">
+        <v>633808.53555435466</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" x14ac:dyDescent="0.4">
       <c r="A25" s="5" t="s">
         <v>11</v>
       </c>
@@ -6888,37 +6718,37 @@
       </c>
       <c r="D25" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.80098207125774</v>
+        <v>7.8009820712577405</v>
       </c>
       <c r="E25" s="6" t="str">
-        <f>IF(OR(C25&gt;3*$G$4,C25&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="0"/>
         <v>ОК</v>
       </c>
       <c r="Y25" s="5">
         <v>5</v>
       </c>
       <c r="Z25" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="AA25" s="8">
         <f>AVERAGEIF(Таблица2[Группа],Таблица1[[#This Row],[группа]],Таблица2[2025])</f>
-        <v>2582.85</v>
-      </c>
-      <c r="AB25" s="8">
+        <v>2582.8499999999995</v>
+      </c>
+      <c r="AB25" s="8" cm="1">
         <f t="array" ref="AB25">_xlfn.VAR.P(_xlfn._xlws.FILTER(Таблица2[2025],Таблица2[Группа]=Таблица1[[#This Row],[группа]]))</f>
-        <v>1886.585</v>
+        <v>1886.5850000000025</v>
       </c>
       <c r="AC25" s="8">
         <f>Таблица1[[#This Row],[частота]]*Таблица1[[#This Row],[групп дисп]]</f>
-        <v>15092.68</v>
+        <v>15092.68000000002</v>
       </c>
       <c r="AD25" s="16">
         <f>Таблица1[[#This Row],[частота]]*(Таблица1[[#This Row],[групп сред]]-$G$3)^2</f>
-        <v>1024053.55847485</v>
-      </c>
-    </row>
-    <row r="26" spans="1:30">
+        <v>1024053.5584748496</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" x14ac:dyDescent="0.4">
       <c r="A26" s="5" t="s">
         <v>7</v>
       </c>
@@ -6931,37 +6761,37 @@
       </c>
       <c r="D26" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.7944112057266</v>
+        <v>7.7944112057266013</v>
       </c>
       <c r="E26" s="6" t="str">
-        <f>IF(OR(C26&gt;3*$G$4,C26&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="0"/>
         <v>ОК</v>
       </c>
       <c r="Y26" s="5">
         <v>6</v>
       </c>
       <c r="Z26" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="AA26" s="8">
         <f>AVERAGEIF(Таблица2[Группа],Таблица1[[#This Row],[группа]],Таблица2[2025])</f>
-        <v>2769.23333333333</v>
-      </c>
-      <c r="AB26" s="8">
+        <v>2769.2333333333336</v>
+      </c>
+      <c r="AB26" s="8" cm="1">
         <f t="array" ref="AB26">_xlfn.VAR.P(_xlfn._xlws.FILTER(Таблица2[2025],Таблица2[Группа]=Таблица1[[#This Row],[группа]]))</f>
-        <v>5906.56222222223</v>
+        <v>5906.5622222222328</v>
       </c>
       <c r="AC26" s="8">
         <f>Таблица1[[#This Row],[частота]]*Таблица1[[#This Row],[групп дисп]]</f>
-        <v>17719.6866666667</v>
+        <v>17719.686666666697</v>
       </c>
       <c r="AD26" s="16">
         <f>Таблица1[[#This Row],[частота]]*(Таблица1[[#This Row],[групп сред]]-$G$3)^2</f>
-        <v>888341.959331172</v>
-      </c>
-    </row>
-    <row r="27" spans="1:30">
+        <v>888341.95933117159</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" x14ac:dyDescent="0.4">
       <c r="A27" s="5" t="s">
         <v>94</v>
       </c>
@@ -6970,28 +6800,28 @@
         <v>4</v>
       </c>
       <c r="C27" s="6">
-        <v>2409.7</v>
+        <v>2409.6999999999998</v>
       </c>
       <c r="D27" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.78725753740846</v>
+        <v>7.7872575374084558</v>
       </c>
       <c r="E27" s="6" t="str">
-        <f>IF(OR(C27&gt;3*$G$4,C27&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="0"/>
         <v>ОК</v>
       </c>
       <c r="Y27" s="5">
         <v>7</v>
       </c>
       <c r="Z27" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AA27" s="8">
         <f>AVERAGEIF(Таблица2[Группа],Таблица1[[#This Row],[группа]],Таблица2[2025])</f>
         <v>2941.2</v>
       </c>
-      <c r="AB27" s="8">
+      <c r="AB27" s="8" cm="1">
         <f t="array" ref="AB27">_xlfn.VAR.P(_xlfn._xlws.FILTER(Таблица2[2025],Таблица2[Группа]=Таблица1[[#This Row],[группа]]))</f>
         <v>0</v>
       </c>
@@ -7001,10 +6831,10 @@
       </c>
       <c r="AD27" s="16">
         <f>Таблица1[[#This Row],[частота]]*(Таблица1[[#This Row],[групп сред]]-$G$3)^2</f>
-        <v>512842.509983775</v>
-      </c>
-    </row>
-    <row r="28" spans="1:30">
+        <v>512842.50998377509</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" x14ac:dyDescent="0.4">
       <c r="A28" s="5" t="s">
         <v>88</v>
       </c>
@@ -7017,37 +6847,37 @@
       </c>
       <c r="D28" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.78555463167432</v>
+        <v>7.7855546316743194</v>
       </c>
       <c r="E28" s="6" t="str">
-        <f>IF(OR(C28&gt;3*$G$4,C28&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="0"/>
         <v>ОК</v>
       </c>
       <c r="Y28" s="5">
         <v>8</v>
       </c>
       <c r="Z28" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="AA28" s="8">
         <f>AVERAGEIF(Таблица2[Группа],Таблица1[[#This Row],[группа]],Таблица2[2025])</f>
-        <v>3167.56666666667</v>
-      </c>
-      <c r="AB28" s="8">
+        <v>3167.5666666666671</v>
+      </c>
+      <c r="AB28" s="8" cm="1">
         <f t="array" ref="AB28">_xlfn.VAR.P(_xlfn._xlws.FILTER(Таблица2[2025],Таблица2[Группа]=Таблица1[[#This Row],[группа]]))</f>
-        <v>3617.2288888889</v>
+        <v>3617.2288888888975</v>
       </c>
       <c r="AC28" s="8">
         <f>Таблица1[[#This Row],[частота]]*Таблица1[[#This Row],[групп дисп]]</f>
-        <v>10851.6866666667</v>
+        <v>10851.686666666692</v>
       </c>
       <c r="AD28" s="16">
         <f>Таблица1[[#This Row],[частота]]*(Таблица1[[#This Row],[групп сред]]-$G$3)^2</f>
-        <v>2664901.21514513</v>
-      </c>
-    </row>
-    <row r="29" spans="1:30">
+        <v>2664901.2151451269</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30" x14ac:dyDescent="0.4">
       <c r="A29" s="5" t="s">
         <v>47</v>
       </c>
@@ -7056,41 +6886,41 @@
         <v>4</v>
       </c>
       <c r="C29" s="6">
-        <v>2403.3</v>
+        <v>2403.3000000000002</v>
       </c>
       <c r="D29" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.78459807188918</v>
+        <v>7.7845980718891807</v>
       </c>
       <c r="E29" s="6" t="str">
-        <f>IF(OR(C29&gt;3*$G$4,C29&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="0"/>
         <v>ОК</v>
       </c>
       <c r="Y29" s="13">
         <v>9</v>
       </c>
       <c r="Z29" s="14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="AA29" s="14">
         <f>AVERAGEIF(Таблица2[Группа],Таблица1[[#This Row],[группа]],Таблица2[2025])</f>
         <v>3385.15</v>
       </c>
-      <c r="AB29" s="14">
+      <c r="AB29" s="14" cm="1">
         <f t="array" ref="AB29">_xlfn.VAR.P(_xlfn._xlws.FILTER(Таблица2[2025],Таблица2[Группа]=Таблица1[[#This Row],[группа]]))</f>
-        <v>5722.92250000001</v>
+        <v>5722.9225000000133</v>
       </c>
       <c r="AC29" s="14">
         <f>Таблица1[[#This Row],[частота]]*Таблица1[[#This Row],[групп дисп]]</f>
-        <v>11445.845</v>
+        <v>11445.845000000027</v>
       </c>
       <c r="AD29" s="17">
         <f>Таблица1[[#This Row],[частота]]*(Таблица1[[#This Row],[групп сред]]-$G$3)^2</f>
-        <v>2691572.2919443</v>
-      </c>
-    </row>
-    <row r="30" spans="1:30">
+        <v>2691572.2919442956</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30" x14ac:dyDescent="0.4">
       <c r="A30" s="5" t="s">
         <v>108</v>
       </c>
@@ -7099,14 +6929,14 @@
         <v>4</v>
       </c>
       <c r="C30" s="6">
-        <v>2401.7</v>
+        <v>2401.6999999999998</v>
       </c>
       <c r="D30" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.78393209891972</v>
+        <v>7.7839320989197169</v>
       </c>
       <c r="E30" s="6" t="str">
-        <f>IF(OR(C30&gt;3*$G$4,C30&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="0"/>
         <v>ОК</v>
       </c>
       <c r="Y30" s="13" t="s">
@@ -7117,14 +6947,14 @@
       <c r="AB30" s="14"/>
       <c r="AC30" s="14">
         <f>SUM(Таблица1[взвеш дисп])</f>
-        <v>368586.605970331</v>
+        <v>368586.60597033123</v>
       </c>
       <c r="AD30" s="17">
         <f>SUBTOTAL(109,Таблица1[взвеш кв откл])</f>
-        <v>11953307.1461227</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+        <v>11953307.146122687</v>
+      </c>
+    </row>
+    <row r="31" spans="1:30" x14ac:dyDescent="0.4">
       <c r="A31" s="5" t="s">
         <v>138</v>
       </c>
@@ -7137,14 +6967,14 @@
       </c>
       <c r="D31" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.78364059622125</v>
+        <v>7.7836405962212529</v>
       </c>
       <c r="E31" s="6" t="str">
-        <f>IF(OR(C31&gt;3*$G$4,C31&lt;$G$4/3),"ВЫБРОС","ОК")</f>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
+        <f t="shared" si="0"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="32" spans="1:30" x14ac:dyDescent="0.4">
       <c r="A32" s="5" t="s">
         <v>14</v>
       </c>
@@ -7153,14 +6983,14 @@
         <v>4</v>
       </c>
       <c r="C32" s="6">
-        <v>2399.3</v>
+        <v>2399.3000000000002</v>
       </c>
       <c r="D32" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.78293230712638</v>
+        <v>7.7829323071263756</v>
       </c>
       <c r="E32" s="6" t="str">
-        <f>IF(OR(C32&gt;3*$G$4,C32&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="0"/>
         <v>ОК</v>
       </c>
       <c r="F32" s="8" t="s">
@@ -7174,7 +7004,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="33" spans="1:28">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A33" s="5" t="s">
         <v>113</v>
       </c>
@@ -7183,14 +7013,14 @@
         <v>4</v>
       </c>
       <c r="C33" s="6">
-        <v>2384.7</v>
+        <v>2384.6999999999998</v>
       </c>
       <c r="D33" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.77682860924718</v>
+        <v>7.7768286092471763</v>
       </c>
       <c r="E33" s="6" t="str">
-        <f>IF(OR(C33&gt;3*$G$4,C33&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="0"/>
         <v>ОК</v>
       </c>
       <c r="F33" s="8" t="s">
@@ -7220,22 +7050,22 @@
       </c>
       <c r="Y33">
         <f>_xlfn.VAR.P(Таблица2[2025])</f>
-        <v>95518.5562177753</v>
+        <v>95518.556217776553</v>
       </c>
       <c r="Z33">
         <f>Таблица1[[#Totals],[взвеш дисп]]/$G$2</f>
-        <v>2857.26051139792</v>
+        <v>2857.2605113979166</v>
       </c>
       <c r="AA33">
         <f>Таблица1[[#Totals],[взвеш кв откл]]/$G$2</f>
-        <v>92661.2957063776</v>
+        <v>92661.295706377408</v>
       </c>
       <c r="AB33">
         <f>Z33+AA33-Y33</f>
-        <v>1.60071067512035e-10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14">
+        <v>-1.2223608791828156E-9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A34" s="5" t="s">
         <v>73</v>
       </c>
@@ -7248,10 +7078,10 @@
       </c>
       <c r="D34" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.77355239663931</v>
+        <v>7.7735523966393059</v>
       </c>
       <c r="E34" s="6" t="str">
-        <f>IF(OR(C34&gt;3*$G$4,C34&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="0"/>
         <v>ОК</v>
       </c>
       <c r="F34" s="8" t="s">
@@ -7269,7 +7099,7 @@
         <v>1751.3</v>
       </c>
       <c r="K34" s="8">
-        <f t="shared" ref="K34:K41" si="4">J34+$G$35</f>
+        <f t="shared" ref="K34:K41" si="5">J34+$G$35</f>
         <v>1964.9875</v>
       </c>
       <c r="L34" s="8">
@@ -7282,10 +7112,10 @@
       </c>
       <c r="N34" s="12">
         <f>Таблица35[[#This Row],[Частота]]/$G$2</f>
-        <v>0.193798449612403</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14">
+        <v>0.19379844961240311</v>
+      </c>
+    </row>
+    <row r="35" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A35" s="5" t="s">
         <v>112</v>
       </c>
@@ -7298,10 +7128,10 @@
       </c>
       <c r="D35" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.76709463440615</v>
+        <v>7.7670946344061536</v>
       </c>
       <c r="E35" s="6" t="str">
-        <f>IF(OR(C35&gt;3*$G$4,C35&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" ref="E35:E66" si="6">IF(OR(C35&gt;3*$G$4,C35&lt;$G$4/3),"ВЫБРОС","ОК")</f>
         <v>ОК</v>
       </c>
       <c r="F35" s="8" t="s">
@@ -7309,7 +7139,7 @@
       </c>
       <c r="G35" s="8">
         <f>(G34-G33)/G32</f>
-        <v>213.6875</v>
+        <v>213.68750000000003</v>
       </c>
       <c r="I35" s="5">
         <v>2</v>
@@ -7319,8 +7149,8 @@
         <v>1964.9875</v>
       </c>
       <c r="K35" s="8">
-        <f t="shared" si="4"/>
-        <v>2178.675</v>
+        <f t="shared" si="5"/>
+        <v>2178.6750000000002</v>
       </c>
       <c r="L35" s="8">
         <f>ROUND((Таблица35[[#This Row],[Ниж. Гран]]+Таблица35[[#This Row],[Верх. Гран.]])/2,2)</f>
@@ -7332,10 +7162,10 @@
       </c>
       <c r="N35" s="8">
         <f>Таблица35[[#This Row],[Частота]]/$G$2</f>
-        <v>0.325581395348837</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14">
+        <v>0.32558139534883723</v>
+      </c>
+    </row>
+    <row r="36" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A36" s="5" t="s">
         <v>74</v>
       </c>
@@ -7351,19 +7181,19 @@
         <v>7.74565194342828</v>
       </c>
       <c r="E36" s="6" t="str">
-        <f>IF(OR(C36&gt;3*$G$4,C36&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="6"/>
         <v>ОК</v>
       </c>
       <c r="I36" s="5">
         <v>3</v>
       </c>
       <c r="J36" s="8">
-        <f t="shared" ref="J36:J41" si="5">K35</f>
-        <v>2178.675</v>
+        <f t="shared" ref="J36:J41" si="7">K35</f>
+        <v>2178.6750000000002</v>
       </c>
       <c r="K36" s="8">
-        <f t="shared" si="4"/>
-        <v>2392.3625</v>
+        <f t="shared" si="5"/>
+        <v>2392.3625000000002</v>
       </c>
       <c r="L36" s="8">
         <f>ROUND((Таблица35[[#This Row],[Ниж. Гран]]+Таблица35[[#This Row],[Верх. Гран.]])/2,2)</f>
@@ -7375,10 +7205,10 @@
       </c>
       <c r="N36" s="8">
         <f>Таблица35[[#This Row],[Частота]]/$G$2</f>
-        <v>0.248062015503876</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14">
+        <v>0.24806201550387597</v>
+      </c>
+    </row>
+    <row r="37" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A37" s="5" t="s">
         <v>99</v>
       </c>
@@ -7391,22 +7221,22 @@
       </c>
       <c r="D37" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.7441799542457</v>
+        <v>7.7441799542457046</v>
       </c>
       <c r="E37" s="6" t="str">
-        <f>IF(OR(C37&gt;3*$G$4,C37&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="6"/>
         <v>ОК</v>
       </c>
       <c r="I37" s="5">
         <v>4</v>
       </c>
       <c r="J37" s="8">
+        <f t="shared" si="7"/>
+        <v>2392.3625000000002</v>
+      </c>
+      <c r="K37" s="8">
         <f t="shared" si="5"/>
-        <v>2392.3625</v>
-      </c>
-      <c r="K37" s="8">
-        <f t="shared" si="4"/>
-        <v>2606.05</v>
+        <v>2606.0500000000002</v>
       </c>
       <c r="L37" s="8">
         <f>ROUND((Таблица35[[#This Row],[Ниж. Гран]]+Таблица35[[#This Row],[Верх. Гран.]])/2,2)</f>
@@ -7418,10 +7248,10 @@
       </c>
       <c r="N37" s="8">
         <f>Таблица35[[#This Row],[Частота]]/$G$2</f>
-        <v>0.147286821705426</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14">
+        <v>0.14728682170542637</v>
+      </c>
+    </row>
+    <row r="38" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A38" s="5" t="s">
         <v>104</v>
       </c>
@@ -7430,26 +7260,26 @@
         <v>3</v>
       </c>
       <c r="C38" s="6">
-        <v>2303.8</v>
+        <v>2303.8000000000002</v>
       </c>
       <c r="D38" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.74231521249241</v>
+        <v>7.7423152124924064</v>
       </c>
       <c r="E38" s="6" t="str">
-        <f>IF(OR(C38&gt;3*$G$4,C38&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="6"/>
         <v>ОК</v>
       </c>
       <c r="I38" s="5">
         <v>5</v>
       </c>
       <c r="J38" s="8">
+        <f t="shared" si="7"/>
+        <v>2606.0500000000002</v>
+      </c>
+      <c r="K38" s="8">
         <f t="shared" si="5"/>
-        <v>2606.05</v>
-      </c>
-      <c r="K38" s="8">
-        <f t="shared" si="4"/>
-        <v>2819.7375</v>
+        <v>2819.7375000000002</v>
       </c>
       <c r="L38" s="8">
         <f>ROUND((Таблица35[[#This Row],[Ниж. Гран]]+Таблица35[[#This Row],[Верх. Гран.]])/2,2)</f>
@@ -7461,10 +7291,10 @@
       </c>
       <c r="N38" s="8">
         <f>Таблица35[[#This Row],[Частота]]/$G$2</f>
-        <v>0.0310077519379845</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14">
+        <v>3.1007751937984496E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A39" s="5" t="s">
         <v>57</v>
       </c>
@@ -7477,22 +7307,22 @@
       </c>
       <c r="D39" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.74175076812946</v>
+        <v>7.7417507681294619</v>
       </c>
       <c r="E39" s="6" t="str">
-        <f>IF(OR(C39&gt;3*$G$4,C39&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="6"/>
         <v>ОК</v>
       </c>
       <c r="I39" s="5">
         <v>6</v>
       </c>
       <c r="J39" s="8">
+        <f t="shared" si="7"/>
+        <v>2819.7375000000002</v>
+      </c>
+      <c r="K39" s="8">
         <f t="shared" si="5"/>
-        <v>2819.7375</v>
-      </c>
-      <c r="K39" s="8">
-        <f t="shared" si="4"/>
-        <v>3033.425</v>
+        <v>3033.4250000000002</v>
       </c>
       <c r="L39" s="8">
         <f>ROUND((Таблица35[[#This Row],[Ниж. Гран]]+Таблица35[[#This Row],[Верх. Гран.]])/2,2)</f>
@@ -7504,10 +7334,10 @@
       </c>
       <c r="N39" s="8">
         <f>Таблица35[[#This Row],[Частота]]/$G$2</f>
-        <v>0.0155038759689922</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14">
+        <v>1.5503875968992248E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A40" s="5" t="s">
         <v>133</v>
       </c>
@@ -7516,26 +7346,26 @@
         <v>3</v>
       </c>
       <c r="C40" s="6">
-        <v>2296.2</v>
+        <v>2296.1999999999998</v>
       </c>
       <c r="D40" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.73901086165971</v>
+        <v>7.7390108616597111</v>
       </c>
       <c r="E40" s="6" t="str">
-        <f>IF(OR(C40&gt;3*$G$4,C40&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="6"/>
         <v>ОК</v>
       </c>
       <c r="I40" s="5">
         <v>7</v>
       </c>
       <c r="J40" s="8">
+        <f t="shared" si="7"/>
+        <v>3033.4250000000002</v>
+      </c>
+      <c r="K40" s="8">
         <f t="shared" si="5"/>
-        <v>3033.425</v>
-      </c>
-      <c r="K40" s="8">
-        <f t="shared" si="4"/>
-        <v>3247.1125</v>
+        <v>3247.1125000000002</v>
       </c>
       <c r="L40" s="8">
         <f>ROUND((Таблица35[[#This Row],[Ниж. Гран]]+Таблица35[[#This Row],[Верх. Гран.]])/2,2)</f>
@@ -7547,10 +7377,10 @@
       </c>
       <c r="N40" s="8">
         <f>Таблица35[[#This Row],[Частота]]/$G$2</f>
-        <v>0.0232558139534884</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14">
+        <v>2.3255813953488372E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A41" s="5" t="s">
         <v>20</v>
       </c>
@@ -7563,21 +7393,21 @@
       </c>
       <c r="D41" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.73783431403723</v>
+        <v>7.7378343140372268</v>
       </c>
       <c r="E41" s="6" t="str">
-        <f>IF(OR(C41&gt;3*$G$4,C41&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="6"/>
         <v>ОК</v>
       </c>
       <c r="I41" s="5">
         <v>8</v>
       </c>
       <c r="J41" s="8">
+        <f t="shared" si="7"/>
+        <v>3247.1125000000002</v>
+      </c>
+      <c r="K41" s="8">
         <f t="shared" si="5"/>
-        <v>3247.1125</v>
-      </c>
-      <c r="K41" s="8">
-        <f t="shared" si="4"/>
         <v>3460.8</v>
       </c>
       <c r="L41" s="8">
@@ -7590,10 +7420,10 @@
       </c>
       <c r="N41" s="8">
         <f>Таблица35[[#This Row],[Частота]]/$G$2</f>
-        <v>0.0155038759689922</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14">
+        <v>1.5503875968992248E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A42" s="5" t="s">
         <v>44</v>
       </c>
@@ -7602,14 +7432,14 @@
         <v>3</v>
       </c>
       <c r="C42" s="6">
-        <v>2288.2</v>
+        <v>2288.1999999999998</v>
       </c>
       <c r="D42" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.73552076126684</v>
+        <v>7.7355207612668435</v>
       </c>
       <c r="E42" s="6" t="str">
-        <f>IF(OR(C42&gt;3*$G$4,C42&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="6"/>
         <v>ОК</v>
       </c>
       <c r="I42" s="13" t="s">
@@ -7617,15 +7447,15 @@
       </c>
       <c r="J42" s="14">
         <f>SUBTOTAL(109,Таблица35[Ниж. Гран])</f>
-        <v>19993.65</v>
+        <v>19993.649999999998</v>
       </c>
       <c r="K42" s="14">
         <f>SUBTOTAL(109,Таблица35[Верх. Гран.])</f>
-        <v>21703.15</v>
+        <v>21703.149999999998</v>
       </c>
       <c r="L42" s="14">
         <f>SUBTOTAL(109,Таблица35[Середина])</f>
-        <v>20848.4</v>
+        <v>20848.399999999998</v>
       </c>
       <c r="M42" s="14">
         <f>SUBTOTAL(109,Таблица35[Частота])</f>
@@ -7633,10 +7463,10 @@
       </c>
       <c r="N42" s="14">
         <f>SUBTOTAL(109,Таблица35[Отн. Частота])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
+        <v>1.0000000000000002</v>
+      </c>
+    </row>
+    <row r="43" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A43" s="5" t="s">
         <v>15</v>
       </c>
@@ -7645,18 +7475,18 @@
         <v>3</v>
       </c>
       <c r="C43" s="6">
-        <v>2285.7</v>
+        <v>2285.6999999999998</v>
       </c>
       <c r="D43" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.73442760214707</v>
+        <v>7.7344276021470737</v>
       </c>
       <c r="E43" s="6" t="str">
-        <f>IF(OR(C43&gt;3*$G$4,C43&lt;$G$4/3),"ВЫБРОС","ОК")</f>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
+        <f t="shared" si="6"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="44" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A44" s="5" t="s">
         <v>114</v>
       </c>
@@ -7669,14 +7499,14 @@
       </c>
       <c r="D44" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.7332456465298</v>
+        <v>7.7332456465297952</v>
       </c>
       <c r="E44" s="6" t="str">
-        <f>IF(OR(C44&gt;3*$G$4,C44&lt;$G$4/3),"ВЫБРОС","ОК")</f>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
+        <f t="shared" si="6"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="45" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A45" s="5" t="s">
         <v>89</v>
       </c>
@@ -7689,14 +7519,14 @@
       </c>
       <c r="D45" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.72859182068297</v>
+        <v>7.728591820682972</v>
       </c>
       <c r="E45" s="6" t="str">
-        <f>IF(OR(C45&gt;3*$G$4,C45&lt;$G$4/3),"ВЫБРОС","ОК")</f>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
+        <f t="shared" si="6"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="46" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A46" s="5" t="s">
         <v>6</v>
       </c>
@@ -7705,18 +7535,18 @@
         <v>3</v>
       </c>
       <c r="C46" s="6">
-        <v>2270.2</v>
+        <v>2270.1999999999998</v>
       </c>
       <c r="D46" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.72762321232124</v>
+        <v>7.7276232123212392</v>
       </c>
       <c r="E46" s="6" t="str">
-        <f>IF(OR(C46&gt;3*$G$4,C46&lt;$G$4/3),"ВЫБРОС","ОК")</f>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
+        <f t="shared" si="6"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="47" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A47" s="5" t="s">
         <v>81</v>
       </c>
@@ -7729,14 +7559,14 @@
       </c>
       <c r="D47" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.7263890795835</v>
+        <v>7.7263890795834982</v>
       </c>
       <c r="E47" s="6" t="str">
-        <f>IF(OR(C47&gt;3*$G$4,C47&lt;$G$4/3),"ВЫБРОС","ОК")</f>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
+        <f t="shared" si="6"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="48" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A48" s="5" t="s">
         <v>12</v>
       </c>
@@ -7749,14 +7579,14 @@
       </c>
       <c r="D48" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.72312009226633</v>
+        <v>7.7231200922663312</v>
       </c>
       <c r="E48" s="6" t="str">
-        <f>IF(OR(C48&gt;3*$G$4,C48&lt;$G$4/3),"ВЫБРОС","ОК")</f>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
+        <f t="shared" si="6"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A49" s="5" t="s">
         <v>111</v>
       </c>
@@ -7769,14 +7599,14 @@
       </c>
       <c r="D49" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.72205758109855</v>
+        <v>7.7220575810985492</v>
       </c>
       <c r="E49" s="6" t="str">
-        <f>IF(OR(C49&gt;3*$G$4,C49&lt;$G$4/3),"ВЫБРОС","ОК")</f>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
+        <f t="shared" si="6"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A50" s="5" t="s">
         <v>96</v>
       </c>
@@ -7789,14 +7619,14 @@
       </c>
       <c r="D50" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.72050605918791</v>
+        <v>7.7205060591879144</v>
       </c>
       <c r="E50" s="6" t="str">
-        <f>IF(OR(C50&gt;3*$G$4,C50&lt;$G$4/3),"ВЫБРОС","ОК")</f>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
+        <f t="shared" si="6"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A51" s="5" t="s">
         <v>100</v>
       </c>
@@ -7809,14 +7639,14 @@
       </c>
       <c r="D51" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.71440970033568</v>
+        <v>7.7144097003356773</v>
       </c>
       <c r="E51" s="6" t="str">
-        <f>IF(OR(C51&gt;3*$G$4,C51&lt;$G$4/3),"ВЫБРОС","ОК")</f>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
+        <f t="shared" si="6"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A52" s="5" t="s">
         <v>65</v>
       </c>
@@ -7825,18 +7655,18 @@
         <v>3</v>
       </c>
       <c r="C52" s="6">
-        <v>2236.7</v>
+        <v>2236.6999999999998</v>
       </c>
       <c r="D52" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.71275684431622</v>
+        <v>7.7127568443162247</v>
       </c>
       <c r="E52" s="6" t="str">
-        <f>IF(OR(C52&gt;3*$G$4,C52&lt;$G$4/3),"ВЫБРОС","ОК")</f>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
+        <f t="shared" si="6"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A53" s="5" t="s">
         <v>23</v>
       </c>
@@ -7849,14 +7679,14 @@
       </c>
       <c r="D53" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.71177276837351</v>
+        <v>7.711772768373506</v>
       </c>
       <c r="E53" s="6" t="str">
-        <f>IF(OR(C53&gt;3*$G$4,C53&lt;$G$4/3),"ВЫБРОС","ОК")</f>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
+        <f t="shared" si="6"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A54" s="5" t="s">
         <v>29</v>
       </c>
@@ -7865,18 +7695,18 @@
         <v>3</v>
       </c>
       <c r="C54" s="6">
-        <v>2234.3</v>
+        <v>2234.3000000000002</v>
       </c>
       <c r="D54" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.71168325888544</v>
+        <v>7.7116832588854409</v>
       </c>
       <c r="E54" s="6" t="str">
-        <f>IF(OR(C54&gt;3*$G$4,C54&lt;$G$4/3),"ВЫБРОС","ОК")</f>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
+        <f t="shared" si="6"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A55" s="5" t="s">
         <v>38</v>
       </c>
@@ -7885,18 +7715,18 @@
         <v>3</v>
       </c>
       <c r="C55" s="6">
-        <v>2228.3</v>
+        <v>2228.3000000000002</v>
       </c>
       <c r="D55" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.70899424189292</v>
+        <v>7.7089942418929223</v>
       </c>
       <c r="E55" s="6" t="str">
-        <f>IF(OR(C55&gt;3*$G$4,C55&lt;$G$4/3),"ВЫБРОС","ОК")</f>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
+        <f t="shared" si="6"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A56" s="5" t="s">
         <v>24</v>
       </c>
@@ -7909,14 +7739,14 @@
       </c>
       <c r="D56" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.70616297019958</v>
+        <v>7.7061629701995757</v>
       </c>
       <c r="E56" s="6" t="str">
-        <f>IF(OR(C56&gt;3*$G$4,C56&lt;$G$4/3),"ВЫБРОС","ОК")</f>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
+        <f t="shared" si="6"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A57" s="5" t="s">
         <v>19</v>
       </c>
@@ -7929,14 +7759,14 @@
       </c>
       <c r="D57" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.70418080899558</v>
+        <v>7.7041808089955843</v>
       </c>
       <c r="E57" s="6" t="str">
-        <f>IF(OR(C57&gt;3*$G$4,C57&lt;$G$4/3),"ВЫБРОС","ОК")</f>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
+        <f t="shared" si="6"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A58" s="5" t="s">
         <v>28</v>
       </c>
@@ -7949,14 +7779,14 @@
       </c>
       <c r="D58" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.70327852615895</v>
+        <v>7.7032785261589485</v>
       </c>
       <c r="E58" s="6" t="str">
-        <f>IF(OR(C58&gt;3*$G$4,C58&lt;$G$4/3),"ВЫБРОС","ОК")</f>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
+        <f t="shared" si="6"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A59" s="5" t="s">
         <v>105</v>
       </c>
@@ -7969,14 +7799,14 @@
       </c>
       <c r="D59" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.70300768247924</v>
+        <v>7.7030076824792362</v>
       </c>
       <c r="E59" s="6" t="str">
-        <f>IF(OR(C59&gt;3*$G$4,C59&lt;$G$4/3),"ВЫБРОС","ОК")</f>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
+        <f t="shared" si="6"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A60" s="5" t="s">
         <v>16</v>
       </c>
@@ -7985,18 +7815,18 @@
         <v>3</v>
       </c>
       <c r="C60" s="6">
-        <v>2211.2</v>
+        <v>2211.1999999999998</v>
       </c>
       <c r="D60" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.70129063357335</v>
+        <v>7.7012906335733504</v>
       </c>
       <c r="E60" s="6" t="str">
-        <f>IF(OR(C60&gt;3*$G$4,C60&lt;$G$4/3),"ВЫБРОС","ОК")</f>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9">
+        <f t="shared" si="6"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A61" s="5" t="s">
         <v>37</v>
       </c>
@@ -8005,14 +7835,14 @@
         <v>3</v>
       </c>
       <c r="C61" s="6">
-        <v>2209.3</v>
+        <v>2209.3000000000002</v>
       </c>
       <c r="D61" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.70043100225698</v>
+        <v>7.7004310022569822</v>
       </c>
       <c r="E61" s="6" t="str">
-        <f>IF(OR(C61&gt;3*$G$4,C61&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="6"/>
         <v>ОК</v>
       </c>
       <c r="F61" s="8" t="s">
@@ -8026,7 +7856,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="62" spans="1:14">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A62" s="5" t="s">
         <v>98</v>
       </c>
@@ -8035,14 +7865,14 @@
         <v>3</v>
       </c>
       <c r="C62" s="6">
-        <v>2198.7</v>
+        <v>2198.6999999999998</v>
       </c>
       <c r="D62" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.69562155559991</v>
+        <v>7.6956215555999137</v>
       </c>
       <c r="E62" s="6" t="str">
-        <f>IF(OR(C62&gt;3*$G$4,C62&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="6"/>
         <v>ОК</v>
       </c>
       <c r="F62" s="8" t="s">
@@ -8071,7 +7901,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="63" spans="1:14">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A63" s="5" t="s">
         <v>127</v>
       </c>
@@ -8080,14 +7910,14 @@
         <v>3</v>
       </c>
       <c r="C63" s="6">
-        <v>2187.2</v>
+        <v>2187.1999999999998</v>
       </c>
       <c r="D63" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.69037746596968</v>
+        <v>7.6903774659696849</v>
       </c>
       <c r="E63" s="6" t="str">
-        <f>IF(OR(C63&gt;3*$G$4,C63&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="6"/>
         <v>ОК</v>
       </c>
       <c r="F63" s="8" t="s">
@@ -8105,7 +7935,7 @@
         <v>1751.3</v>
       </c>
       <c r="K63" s="8">
-        <f t="shared" ref="K63:K72" si="6">J63+$G$64</f>
+        <f t="shared" ref="K63:K72" si="8">J63+$G$64</f>
         <v>1922.25</v>
       </c>
       <c r="L63" s="8">
@@ -8118,10 +7948,10 @@
       </c>
       <c r="N63" s="12">
         <f>Таблица356[[#This Row],[Частота]]/$G$2</f>
-        <v>0.108527131782946</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14">
+        <v>0.10852713178294573</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A64" s="5" t="s">
         <v>87</v>
       </c>
@@ -8130,14 +7960,14 @@
         <v>3</v>
       </c>
       <c r="C64" s="6">
-        <v>2182.8</v>
+        <v>2182.8000000000002</v>
       </c>
       <c r="D64" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.68836373531208</v>
+        <v>7.6883637353120768</v>
       </c>
       <c r="E64" s="6" t="str">
-        <f>IF(OR(C64&gt;3*$G$4,C64&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="6"/>
         <v>ОК</v>
       </c>
       <c r="F64" s="8" t="s">
@@ -8145,7 +7975,7 @@
       </c>
       <c r="G64" s="8">
         <f>(G63-G62)/G61</f>
-        <v>170.95</v>
+        <v>170.95000000000002</v>
       </c>
       <c r="I64" s="5">
         <v>2</v>
@@ -8155,8 +7985,8 @@
         <v>1922.25</v>
       </c>
       <c r="K64" s="8">
-        <f t="shared" si="6"/>
-        <v>2093.2</v>
+        <f t="shared" si="8"/>
+        <v>2093.1999999999998</v>
       </c>
       <c r="L64" s="8">
         <f>ROUND((Таблица356[[#This Row],[Ниж. Гран]]+Таблица356[[#This Row],[Верх. Гран.]])/2,2)</f>
@@ -8168,10 +7998,10 @@
       </c>
       <c r="N64" s="8">
         <f>Таблица356[[#This Row],[Частота]]/$G$2</f>
-        <v>0.24031007751938</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14">
+        <v>0.24031007751937986</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A65" s="5" t="s">
         <v>118</v>
       </c>
@@ -8184,26 +8014,26 @@
       </c>
       <c r="D65" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.68409405042885</v>
+        <v>7.6840940504288469</v>
       </c>
       <c r="E65" s="6" t="str">
-        <f>IF(OR(C65&gt;3*$G$4,C65&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="6"/>
         <v>ОК</v>
       </c>
       <c r="I65" s="5">
         <v>3</v>
       </c>
       <c r="J65" s="8">
-        <f t="shared" ref="J65:J72" si="7">K64</f>
-        <v>2093.2</v>
+        <f t="shared" ref="J65:J72" si="9">K64</f>
+        <v>2093.1999999999998</v>
       </c>
       <c r="K65" s="8">
-        <f t="shared" si="6"/>
-        <v>2264.15</v>
+        <f t="shared" si="8"/>
+        <v>2264.1499999999996</v>
       </c>
       <c r="L65" s="8">
         <f>ROUND((Таблица356[[#This Row],[Ниж. Гран]]+Таблица356[[#This Row],[Верх. Гран.]])/2,2)</f>
-        <v>2178.68</v>
+        <v>2178.6799999999998</v>
       </c>
       <c r="M65" s="16">
         <f>IF(Таблица356[[#This Row],[Интервал]]=MAX(Таблица356[Интервал]),COUNTIFS(Таблица2[2025],"&gt;="&amp;Таблица356[[#This Row],[Ниж. Гран]],Таблица2[2025],"&lt;="&amp;Таблица356[[#This Row],[Верх. Гран.]]),COUNTIFS(Таблица2[2025],"&gt;="&amp;Таблица356[[#This Row],[Ниж. Гран]],Таблица2[2025],"&lt;"&amp;Таблица356[[#This Row],[Верх. Гран.]]))</f>
@@ -8211,10 +8041,10 @@
       </c>
       <c r="N65" s="8">
         <f>Таблица356[[#This Row],[Частота]]/$G$2</f>
-        <v>0.302325581395349</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14">
+        <v>0.30232558139534882</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A66" s="5" t="s">
         <v>77</v>
       </c>
@@ -8227,22 +8057,22 @@
       </c>
       <c r="D66" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.6744316928302</v>
+        <v>7.6744316928301979</v>
       </c>
       <c r="E66" s="6" t="str">
-        <f>IF(OR(C66&gt;3*$G$4,C66&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" si="6"/>
         <v>ОК</v>
       </c>
       <c r="I66" s="5">
         <v>4</v>
       </c>
       <c r="J66" s="8">
-        <f t="shared" si="7"/>
-        <v>2264.15</v>
+        <f t="shared" si="9"/>
+        <v>2264.1499999999996</v>
       </c>
       <c r="K66" s="8">
-        <f t="shared" si="6"/>
-        <v>2435.1</v>
+        <f t="shared" si="8"/>
+        <v>2435.0999999999995</v>
       </c>
       <c r="L66" s="8">
         <f>ROUND((Таблица356[[#This Row],[Ниж. Гран]]+Таблица356[[#This Row],[Верх. Гран.]])/2,2)</f>
@@ -8254,10 +8084,10 @@
       </c>
       <c r="N66" s="8">
         <f>Таблица356[[#This Row],[Частота]]/$G$2</f>
-        <v>0.170542635658915</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14">
+        <v>0.17054263565891473</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A67" s="5" t="s">
         <v>34</v>
       </c>
@@ -8270,10 +8100,10 @@
       </c>
       <c r="D67" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.67387407199791</v>
+        <v>7.6738740719979051</v>
       </c>
       <c r="E67" s="6" t="str">
-        <f t="shared" ref="E67:E98" si="8">IF(OR(C67&gt;3*$G$4,C67&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" ref="E67:E98" si="10">IF(OR(C67&gt;3*$G$4,C67&lt;$G$4/3),"ВЫБРОС","ОК")</f>
         <v>ОК</v>
       </c>
       <c r="F67" t="s">
@@ -8286,12 +8116,12 @@
         <v>5</v>
       </c>
       <c r="J67" s="8">
-        <f t="shared" si="7"/>
-        <v>2435.1</v>
+        <f t="shared" si="9"/>
+        <v>2435.0999999999995</v>
       </c>
       <c r="K67" s="8">
-        <f t="shared" si="6"/>
-        <v>2606.05</v>
+        <f t="shared" si="8"/>
+        <v>2606.0499999999993</v>
       </c>
       <c r="L67" s="8">
         <f>ROUND((Таблица356[[#This Row],[Ниж. Гран]]+Таблица356[[#This Row],[Верх. Гран.]])/2,2)</f>
@@ -8303,10 +8133,10 @@
       </c>
       <c r="N67" s="8">
         <f>Таблица356[[#This Row],[Частота]]/$G$2</f>
-        <v>0.0930232558139535</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14">
+        <v>9.3023255813953487E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A68" s="5" t="s">
         <v>95</v>
       </c>
@@ -8319,22 +8149,22 @@
       </c>
       <c r="D68" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.6731766084121</v>
+        <v>7.6731766084121018</v>
       </c>
       <c r="E68" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>ОК</v>
       </c>
       <c r="I68" s="5">
         <v>6</v>
       </c>
       <c r="J68" s="8">
-        <f t="shared" si="7"/>
-        <v>2606.05</v>
+        <f t="shared" si="9"/>
+        <v>2606.0499999999993</v>
       </c>
       <c r="K68" s="8">
-        <f t="shared" si="6"/>
-        <v>2777</v>
+        <f t="shared" si="8"/>
+        <v>2776.9999999999991</v>
       </c>
       <c r="L68" s="8">
         <f>ROUND((Таблица356[[#This Row],[Ниж. Гран]]+Таблица356[[#This Row],[Верх. Гран.]])/2,2)</f>
@@ -8346,10 +8176,10 @@
       </c>
       <c r="N68" s="8">
         <f>Таблица356[[#This Row],[Частота]]/$G$2</f>
-        <v>0.0310077519379845</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14">
+        <v>3.1007751937984496E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A69" s="5" t="s">
         <v>140</v>
       </c>
@@ -8358,26 +8188,26 @@
         <v>3</v>
       </c>
       <c r="C69" s="6">
-        <v>2149.7</v>
+        <v>2149.6999999999998</v>
       </c>
       <c r="D69" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.67308357650209</v>
+        <v>7.6730835765020897</v>
       </c>
       <c r="E69" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>ОК</v>
       </c>
       <c r="I69" s="5">
         <v>7</v>
       </c>
       <c r="J69" s="8">
-        <f t="shared" si="7"/>
-        <v>2777</v>
+        <f t="shared" si="9"/>
+        <v>2776.9999999999991</v>
       </c>
       <c r="K69" s="8">
-        <f t="shared" si="6"/>
-        <v>2947.95</v>
+        <f t="shared" si="8"/>
+        <v>2947.9499999999989</v>
       </c>
       <c r="L69" s="8">
         <f>ROUND((Таблица356[[#This Row],[Ниж. Гран]]+Таблица356[[#This Row],[Верх. Гран.]])/2,2)</f>
@@ -8389,10 +8219,10 @@
       </c>
       <c r="N69" s="8">
         <f>Таблица356[[#This Row],[Частота]]/$G$2</f>
-        <v>0.0155038759689922</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14">
+        <v>1.5503875968992248E-2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A70" s="5" t="s">
         <v>58</v>
       </c>
@@ -8405,22 +8235,22 @@
       </c>
       <c r="D70" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.67201308700004</v>
+        <v>7.6720130870000354</v>
       </c>
       <c r="E70" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>ОК</v>
       </c>
       <c r="I70" s="5">
         <v>8</v>
       </c>
       <c r="J70" s="8">
-        <f t="shared" si="7"/>
-        <v>2947.95</v>
+        <f t="shared" si="9"/>
+        <v>2947.9499999999989</v>
       </c>
       <c r="K70" s="8">
-        <f t="shared" si="6"/>
-        <v>3118.9</v>
+        <f t="shared" si="8"/>
+        <v>3118.8999999999987</v>
       </c>
       <c r="L70" s="8">
         <f>ROUND((Таблица356[[#This Row],[Ниж. Гран]]+Таблица356[[#This Row],[Верх. Гран.]])/2,2)</f>
@@ -8432,10 +8262,10 @@
       </c>
       <c r="N70" s="8">
         <f>Таблица356[[#This Row],[Частота]]/$G$2</f>
-        <v>0.00775193798449612</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14">
+        <v>7.7519379844961239E-3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A71" s="5" t="s">
         <v>18</v>
       </c>
@@ -8448,22 +8278,22 @@
       </c>
       <c r="D71" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.66739220081091</v>
+        <v>7.667392200810915</v>
       </c>
       <c r="E71" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>ОК</v>
       </c>
       <c r="I71" s="5">
         <v>9</v>
       </c>
       <c r="J71" s="8">
-        <f t="shared" si="7"/>
-        <v>3118.9</v>
+        <f t="shared" si="9"/>
+        <v>3118.8999999999987</v>
       </c>
       <c r="K71" s="21">
-        <f t="shared" si="6"/>
-        <v>3289.85</v>
+        <f t="shared" si="8"/>
+        <v>3289.8499999999985</v>
       </c>
       <c r="L71" s="21">
         <f>ROUND((Таблица356[[#This Row],[Ниж. Гран]]+Таблица356[[#This Row],[Верх. Гран.]])/2,2)</f>
@@ -8475,10 +8305,10 @@
       </c>
       <c r="N71" s="21">
         <f>Таблица356[[#This Row],[Частота]]/$G$2</f>
-        <v>0.0155038759689922</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14">
+        <v>1.5503875968992248E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A72" s="5" t="s">
         <v>10</v>
       </c>
@@ -8491,22 +8321,22 @@
       </c>
       <c r="D72" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.66486268850096</v>
+        <v>7.6648626885009588</v>
       </c>
       <c r="E72" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>ОК</v>
       </c>
       <c r="I72" s="5">
         <v>10</v>
       </c>
       <c r="J72" s="8">
-        <f t="shared" si="7"/>
-        <v>3289.85</v>
+        <f t="shared" si="9"/>
+        <v>3289.8499999999985</v>
       </c>
       <c r="K72" s="21">
-        <f t="shared" si="6"/>
-        <v>3460.8</v>
+        <f t="shared" si="8"/>
+        <v>3460.7999999999984</v>
       </c>
       <c r="L72" s="21">
         <f>ROUND((Таблица356[[#This Row],[Ниж. Гран]]+Таблица356[[#This Row],[Верх. Гран.]])/2,2)</f>
@@ -8518,10 +8348,10 @@
       </c>
       <c r="N72" s="21">
         <f>Таблица356[[#This Row],[Частота]]/$G$2</f>
-        <v>0.0155038759689922</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14">
+        <v>1.5503875968992248E-2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A73" s="5" t="s">
         <v>83</v>
       </c>
@@ -8534,10 +8364,10 @@
       </c>
       <c r="D73" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.66453431978686</v>
+        <v>7.6645343197868554</v>
       </c>
       <c r="E73" s="6" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>ОК</v>
       </c>
       <c r="I73" s="13" t="s">
@@ -8545,15 +8375,15 @@
       </c>
       <c r="J73" s="14">
         <f>SUBTOTAL(109,Таблица356[Ниж. Гран])</f>
-        <v>25205.75</v>
+        <v>25205.749999999996</v>
       </c>
       <c r="K73" s="14">
         <f>SUBTOTAL(109,Таблица356[Верх. Гран.])</f>
-        <v>26915.25</v>
+        <v>26915.249999999993</v>
       </c>
       <c r="L73" s="14">
         <f>SUBTOTAL(109,Таблица356[Середина])</f>
-        <v>26060.55</v>
+        <v>26060.550000000003</v>
       </c>
       <c r="M73" s="14">
         <f>SUBTOTAL(109,Таблица356[Частота])</f>
@@ -8561,10 +8391,10 @@
       </c>
       <c r="N73" s="14">
         <f>SUBTOTAL(109,Таблица356[Отн. Частота])</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
+        <v>1.0000000000000002</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A74" s="5" t="s">
         <v>17</v>
       </c>
@@ -8573,18 +8403,18 @@
         <v>2</v>
       </c>
       <c r="C74" s="6">
-        <v>2128.7</v>
+        <v>2128.6999999999998</v>
       </c>
       <c r="D74" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.66326674373863</v>
+        <v>7.6632667437386326</v>
       </c>
       <c r="E74" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
+        <f t="shared" si="10"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A75" s="5" t="s">
         <v>93</v>
       </c>
@@ -8593,18 +8423,18 @@
         <v>2</v>
       </c>
       <c r="C75" s="6">
-        <v>2127.3</v>
+        <v>2127.3000000000002</v>
       </c>
       <c r="D75" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.66260884897806</v>
+        <v>7.6626088489780608</v>
       </c>
       <c r="E75" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
+        <f t="shared" si="10"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A76" s="5" t="s">
         <v>86</v>
       </c>
@@ -8613,18 +8443,18 @@
         <v>2</v>
       </c>
       <c r="C76" s="6">
-        <v>2125.2</v>
+        <v>2125.1999999999998</v>
       </c>
       <c r="D76" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.66162119457679</v>
+        <v>7.6616211945767878</v>
       </c>
       <c r="E76" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
+        <f t="shared" si="10"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A77" s="5" t="s">
         <v>129</v>
       </c>
@@ -8633,18 +8463,18 @@
         <v>2</v>
       </c>
       <c r="C77" s="6">
-        <v>2123.2</v>
+        <v>2123.1999999999998</v>
       </c>
       <c r="D77" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.66067966357794</v>
+        <v>7.6606796635779428</v>
       </c>
       <c r="E77" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
+        <f t="shared" si="10"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A78" s="5" t="s">
         <v>33</v>
       </c>
@@ -8657,14 +8487,14 @@
       </c>
       <c r="D78" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.66011431917393</v>
+        <v>7.6601143191739283</v>
       </c>
       <c r="E78" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
+        <f t="shared" si="10"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A79" s="5" t="s">
         <v>53</v>
       </c>
@@ -8677,14 +8507,14 @@
       </c>
       <c r="D79" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.65756630665962</v>
+        <v>7.657566306659624</v>
       </c>
       <c r="E79" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
+        <f t="shared" si="10"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A80" s="5" t="s">
         <v>56</v>
       </c>
@@ -8697,14 +8527,14 @@
       </c>
       <c r="D80" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.65681009148038</v>
+        <v>7.6568100914803781</v>
       </c>
       <c r="E80" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
+        <f t="shared" si="10"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A81" s="5" t="s">
         <v>13</v>
       </c>
@@ -8717,14 +8547,14 @@
       </c>
       <c r="D81" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.65662094829843</v>
+        <v>7.6566209482984258</v>
       </c>
       <c r="E81" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
+        <f t="shared" si="10"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A82" s="5" t="s">
         <v>78</v>
       </c>
@@ -8733,18 +8563,18 @@
         <v>2</v>
       </c>
       <c r="C82" s="6">
-        <v>2110.2</v>
+        <v>2110.1999999999998</v>
       </c>
       <c r="D82" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.65453800870799</v>
+        <v>7.6545380087079913</v>
       </c>
       <c r="E82" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
+        <f t="shared" si="10"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A83" s="5" t="s">
         <v>85</v>
       </c>
@@ -8757,14 +8587,14 @@
       </c>
       <c r="D83" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.65249820818573</v>
+        <v>7.6524982081857331</v>
       </c>
       <c r="E83" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
+        <f t="shared" si="10"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A84" s="5" t="s">
         <v>122</v>
       </c>
@@ -8777,14 +8607,14 @@
       </c>
       <c r="D84" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.6508823918471</v>
+        <v>7.6508823918471034</v>
       </c>
       <c r="E84" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
+        <f t="shared" si="10"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A85" s="5" t="s">
         <v>30</v>
       </c>
@@ -8797,14 +8627,14 @@
       </c>
       <c r="D85" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.650216296095</v>
+        <v>7.6502162960950031</v>
       </c>
       <c r="E85" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
+        <f t="shared" si="10"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A86" s="5" t="s">
         <v>80</v>
       </c>
@@ -8817,14 +8647,14 @@
       </c>
       <c r="D86" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.64854911300944</v>
+        <v>7.6485491130094356</v>
       </c>
       <c r="E86" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
+        <f t="shared" si="10"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A87" s="5" t="s">
         <v>67</v>
       </c>
@@ -8837,14 +8667,14 @@
       </c>
       <c r="D87" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.64017124846278</v>
+        <v>7.6401712484627824</v>
       </c>
       <c r="E87" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
+        <f t="shared" si="10"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A88" s="5" t="s">
         <v>39</v>
       </c>
@@ -8853,18 +8683,18 @@
         <v>2</v>
       </c>
       <c r="C88" s="6">
-        <v>2075.8</v>
+        <v>2075.8000000000002</v>
       </c>
       <c r="D88" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.63810190053119</v>
+        <v>7.638101900531189</v>
       </c>
       <c r="E88" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5">
+        <f t="shared" si="10"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A89" s="5" t="s">
         <v>51</v>
       </c>
@@ -8873,18 +8703,18 @@
         <v>2</v>
       </c>
       <c r="C89" s="6">
-        <v>2066.7</v>
+        <v>2066.6999999999998</v>
       </c>
       <c r="D89" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.63370841126726</v>
+        <v>7.6337084112672597</v>
       </c>
       <c r="E89" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
+        <f t="shared" si="10"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A90" s="5" t="s">
         <v>120</v>
       </c>
@@ -8897,14 +8727,14 @@
       </c>
       <c r="D90" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.63336964967958</v>
+        <v>7.633369649679584</v>
       </c>
       <c r="E90" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5">
+        <f t="shared" si="10"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A91" s="5" t="s">
         <v>32</v>
       </c>
@@ -8913,18 +8743,18 @@
         <v>2</v>
       </c>
       <c r="C91" s="6">
-        <v>2060.7</v>
+        <v>2060.6999999999998</v>
       </c>
       <c r="D91" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.63080100988795</v>
+        <v>7.6308010098879455</v>
       </c>
       <c r="E91" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5">
+        <f t="shared" si="10"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A92" s="5" t="s">
         <v>126</v>
       </c>
@@ -8937,14 +8767,14 @@
       </c>
       <c r="D92" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.63046126178363</v>
+        <v>7.6304612617836272</v>
       </c>
       <c r="E92" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5">
+        <f t="shared" si="10"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A93" s="5" t="s">
         <v>70</v>
       </c>
@@ -8957,14 +8787,14 @@
       </c>
       <c r="D93" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.62021477057445</v>
+        <v>7.6202147705744547</v>
       </c>
       <c r="E93" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5">
+        <f t="shared" si="10"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A94" s="5" t="s">
         <v>42</v>
       </c>
@@ -8977,14 +8807,14 @@
       </c>
       <c r="D94" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.62006762880309</v>
+        <v>7.6200676288030929</v>
       </c>
       <c r="E94" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5">
+        <f t="shared" si="10"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A95" s="5" t="s">
         <v>82</v>
       </c>
@@ -9000,11 +8830,11 @@
         <v>7.61815281294861</v>
       </c>
       <c r="E95" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5">
+        <f t="shared" si="10"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A96" s="5" t="s">
         <v>75</v>
       </c>
@@ -9017,14 +8847,14 @@
       </c>
       <c r="D96" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.6110012942195</v>
+        <v>7.6110012942194967</v>
       </c>
       <c r="E96" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5">
+        <f t="shared" si="10"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A97" s="5" t="s">
         <v>124</v>
       </c>
@@ -9037,14 +8867,14 @@
       </c>
       <c r="D97" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.61025855446611</v>
+        <v>7.6102585544661077</v>
       </c>
       <c r="E97" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5">
+        <f t="shared" si="10"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A98" s="5" t="s">
         <v>54</v>
       </c>
@@ -9057,14 +8887,14 @@
       </c>
       <c r="D98" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.60514345379934</v>
+        <v>7.6051434537993368</v>
       </c>
       <c r="E98" s="6" t="str">
-        <f t="shared" si="8"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5">
+        <f t="shared" si="10"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A99" s="5" t="s">
         <v>55</v>
       </c>
@@ -9077,14 +8907,14 @@
       </c>
       <c r="D99" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.60349908538935</v>
+        <v>7.6034990853893483</v>
       </c>
       <c r="E99" s="6" t="str">
-        <f t="shared" ref="E99:E130" si="9">IF(OR(C99&gt;3*$G$4,C99&lt;$G$4/3),"ВЫБРОС","ОК")</f>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5">
+        <f t="shared" ref="E99:E130" si="11">IF(OR(C99&gt;3*$G$4,C99&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A100" s="5" t="s">
         <v>21</v>
       </c>
@@ -9097,14 +8927,14 @@
       </c>
       <c r="D100" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.60235140930719</v>
+        <v>7.6023514093071869</v>
       </c>
       <c r="E100" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5">
+        <f t="shared" si="11"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A101" s="5" t="s">
         <v>41</v>
       </c>
@@ -9117,14 +8947,14 @@
       </c>
       <c r="D101" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.60215167894251</v>
+        <v>7.6021516789425139</v>
       </c>
       <c r="E101" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5">
+        <f t="shared" si="11"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A102" s="5" t="s">
         <v>119</v>
       </c>
@@ -9137,14 +8967,14 @@
       </c>
       <c r="D102" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.60015217815138</v>
+        <v>7.6001521781513786</v>
       </c>
       <c r="E102" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5">
+        <f t="shared" si="11"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A103" s="5" t="s">
         <v>35</v>
       </c>
@@ -9157,14 +8987,14 @@
       </c>
       <c r="D103" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.59478377853391</v>
+        <v>7.5947837785339054</v>
       </c>
       <c r="E103" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5">
+        <f t="shared" si="11"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A104" s="5" t="s">
         <v>63</v>
       </c>
@@ -9180,11 +9010,11 @@
         <v>7.59231569860476</v>
       </c>
       <c r="E104" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5">
+        <f t="shared" si="11"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A105" s="5" t="s">
         <v>26</v>
       </c>
@@ -9197,14 +9027,14 @@
       </c>
       <c r="D105" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.59039747489693</v>
+        <v>7.5903974748969345</v>
       </c>
       <c r="E105" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5">
+        <f t="shared" si="11"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A106" s="5" t="s">
         <v>9</v>
       </c>
@@ -9217,14 +9047,14 @@
       </c>
       <c r="D106" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.58670211014094</v>
+        <v>7.5867021101409406</v>
       </c>
       <c r="E106" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5">
+        <f t="shared" si="11"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A107" s="5" t="s">
         <v>52</v>
       </c>
@@ -9237,14 +9067,14 @@
       </c>
       <c r="D107" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.58151574574189</v>
+        <v>7.5815157457418918</v>
       </c>
       <c r="E107" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5">
+        <f t="shared" si="11"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A108" s="5" t="s">
         <v>125</v>
       </c>
@@ -9257,14 +9087,14 @@
       </c>
       <c r="D108" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.57727552891093</v>
+        <v>7.5772755289109259</v>
       </c>
       <c r="E108" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5">
+        <f t="shared" si="11"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A109" s="5" t="s">
         <v>121</v>
       </c>
@@ -9277,14 +9107,14 @@
       </c>
       <c r="D109" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.57681466401299</v>
+        <v>7.5768146640129928</v>
       </c>
       <c r="E109" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5">
+        <f t="shared" si="11"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A110" s="5" t="s">
         <v>61</v>
       </c>
@@ -9297,14 +9127,14 @@
       </c>
       <c r="D110" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.57466114833686</v>
+        <v>7.5746611483368556</v>
       </c>
       <c r="E110" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5">
+        <f t="shared" si="11"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A111" s="5" t="s">
         <v>79</v>
       </c>
@@ -9317,14 +9147,14 @@
       </c>
       <c r="D111" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.57090706200668</v>
+        <v>7.5709070620066816</v>
       </c>
       <c r="E111" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5">
+        <f t="shared" si="11"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A112" s="5" t="s">
         <v>130</v>
       </c>
@@ -9337,14 +9167,14 @@
       </c>
       <c r="D112" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.57059787927723</v>
+        <v>7.5705978792772264</v>
       </c>
       <c r="E112" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5">
+        <f t="shared" si="11"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A113" s="5" t="s">
         <v>31</v>
       </c>
@@ -9357,14 +9187,14 @@
       </c>
       <c r="D113" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.56568970378634</v>
+        <v>7.5656897037863375</v>
       </c>
       <c r="E113" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5">
+        <f t="shared" si="11"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A114" s="5" t="s">
         <v>69</v>
       </c>
@@ -9377,14 +9207,14 @@
       </c>
       <c r="D114" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.56418660660542</v>
+        <v>7.5641866066054231</v>
       </c>
       <c r="E114" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5">
+        <f t="shared" si="11"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A115" s="5" t="s">
         <v>46</v>
       </c>
@@ -9397,14 +9227,14 @@
       </c>
       <c r="D115" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.56371966841437</v>
+        <v>7.5637196684143664</v>
       </c>
       <c r="E115" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5">
+        <f t="shared" si="11"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A116" s="5" t="s">
         <v>137</v>
       </c>
@@ -9417,14 +9247,14 @@
       </c>
       <c r="D116" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.5623695098253</v>
+        <v>7.5623695098252988</v>
       </c>
       <c r="E116" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5">
+        <f t="shared" si="11"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A117" s="5" t="s">
         <v>136</v>
       </c>
@@ -9437,14 +9267,14 @@
       </c>
       <c r="D117" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.56231754422651</v>
+        <v>7.5623175442265129</v>
       </c>
       <c r="E117" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5">
+        <f t="shared" si="11"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A118" s="5" t="s">
         <v>132</v>
       </c>
@@ -9457,14 +9287,14 @@
       </c>
       <c r="D118" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.55648024198934</v>
+        <v>7.5564802419893358</v>
       </c>
       <c r="E118" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5">
+        <f t="shared" si="11"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A119" s="5" t="s">
         <v>60</v>
       </c>
@@ -9477,14 +9307,14 @@
       </c>
       <c r="D119" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.55255219860104</v>
+        <v>7.5525521986010355</v>
       </c>
       <c r="E119" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5">
+        <f t="shared" si="11"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A120" s="5" t="s">
         <v>27</v>
       </c>
@@ -9497,14 +9327,14 @@
       </c>
       <c r="D120" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.54892472044937</v>
+        <v>7.548924720449369</v>
       </c>
       <c r="E120" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5">
+        <f t="shared" si="11"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A121" s="5" t="s">
         <v>50</v>
       </c>
@@ -9517,14 +9347,14 @@
       </c>
       <c r="D121" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.54755442404016</v>
+        <v>7.5475544240401575</v>
       </c>
       <c r="E121" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5">
+        <f t="shared" si="11"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A122" s="5" t="s">
         <v>135</v>
       </c>
@@ -9537,14 +9367,14 @@
       </c>
       <c r="D122" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.54713241633225</v>
+        <v>7.5471324163322544</v>
       </c>
       <c r="E122" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5">
+        <f t="shared" si="11"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A123" s="5" t="s">
         <v>123</v>
       </c>
@@ -9557,14 +9387,14 @@
       </c>
       <c r="D123" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.54512544407308</v>
+        <v>7.5451254440730837</v>
       </c>
       <c r="E123" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5">
+        <f t="shared" si="11"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A124" s="5" t="s">
         <v>64</v>
       </c>
@@ -9577,14 +9407,14 @@
       </c>
       <c r="D124" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.53657724898552</v>
+        <v>7.5365772489855249</v>
       </c>
       <c r="E124" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5">
+        <f t="shared" si="11"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A125" s="5" t="s">
         <v>36</v>
       </c>
@@ -9597,14 +9427,14 @@
       </c>
       <c r="D125" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.53358675225722</v>
+        <v>7.5335867522572153</v>
       </c>
       <c r="E125" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5">
+        <f t="shared" si="11"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A126" s="5" t="s">
         <v>134</v>
       </c>
@@ -9617,14 +9447,14 @@
       </c>
       <c r="D126" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.52951386345443</v>
+        <v>7.5295138634544294</v>
       </c>
       <c r="E126" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5">
+        <f t="shared" si="11"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A127" s="5" t="s">
         <v>43</v>
       </c>
@@ -9637,14 +9467,14 @@
       </c>
       <c r="D127" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.52450725828837</v>
+        <v>7.5245072582883692</v>
       </c>
       <c r="E127" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5">
+        <f t="shared" si="11"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A128" s="5" t="s">
         <v>128</v>
       </c>
@@ -9657,14 +9487,14 @@
       </c>
       <c r="D128" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.52012614951479</v>
+        <v>7.5201261495147946</v>
       </c>
       <c r="E128" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5">
+        <f t="shared" si="11"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A129" s="5" t="s">
         <v>59</v>
       </c>
@@ -9677,14 +9507,14 @@
       </c>
       <c r="D129" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.51893289667483</v>
+        <v>7.5189328966748317</v>
       </c>
       <c r="E129" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5">
+        <f t="shared" si="11"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A130" s="5" t="s">
         <v>40</v>
       </c>
@@ -9697,14 +9527,14 @@
       </c>
       <c r="D130" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.51207124583547</v>
+        <v>7.5120712458354664</v>
       </c>
       <c r="E130" s="6" t="str">
-        <f t="shared" si="9"/>
-        <v>ОК</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5">
+        <f t="shared" si="11"/>
+        <v>ОК</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A131" s="13" t="s">
         <v>45</v>
       </c>
@@ -9717,19 +9547,18 @@
       </c>
       <c r="D131" s="6">
         <f>LN(Таблица2[[#This Row],[2025]])</f>
-        <v>7.46811364827862</v>
+        <v>7.468113648278619</v>
       </c>
       <c r="E131" s="6" t="str">
-        <f t="shared" ref="E131" si="10">IF(OR(C131&gt;3*$G$4,C131&lt;$G$4/3),"ВЫБРОС","ОК")</f>
+        <f t="shared" ref="E131" si="12">IF(OR(C131&gt;3*$G$4,C131&lt;$G$4/3),"ВЫБРОС","ОК")</f>
         <v>ОК</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A3:C131">
-    <sortCondition ref="C3:C131" descending="1"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:C131">
+    <sortCondition descending="1" ref="C3:C131"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
   <tableParts count="5">
     <tablePart r:id="rId2"/>
@@ -9742,12 +9571,10 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>